--- a/data/kost.xlsx
+++ b/data/kost.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\SEMESTER 6\PRAK. SIGTER\PROJECT AKHIR\STUDENT SURVIVAL MAP\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99D23832-1490-47C2-BD38-5860CDAB3A0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6F6449E-C02D-4987-8362-05B7C7904211}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{26F0A93B-5A06-4626-B5C9-AA29E6F5E080}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1268" uniqueCount="847">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1370" uniqueCount="851">
   <si>
     <t>Id</t>
   </si>
@@ -2566,13 +2566,25 @@
   </si>
   <si>
     <t>images\KS101.jpg</t>
+  </si>
+  <si>
+    <t>Mahal</t>
+  </si>
+  <si>
+    <t>Murah</t>
+  </si>
+  <si>
+    <t>Menengah</t>
+  </si>
+  <si>
+    <t>Kategori Harga</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2652,6 +2664,19 @@
       <charset val="1"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -2679,7 +2704,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -2702,12 +2727,42 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -2763,7 +2818,15 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3079,7 +3142,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D6A42FB-15A6-4E06-A906-A247DB6CDD70}">
-  <dimension ref="A1:N102"/>
+  <dimension ref="A1:O102"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
@@ -3089,16 +3152,17 @@
     <col min="5" max="5" width="17.88671875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="145.5546875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="32.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="22.88671875" style="25" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="22.5546875" style="25" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="22.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="22.5546875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="52.88671875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="47" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.77734375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="52.88671875" customWidth="1"/>
+    <col min="12" max="12" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="47" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17.77734375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="31.2">
+    <row r="1" spans="1:15" ht="31.8" thickBot="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3129,20 +3193,23 @@
       <c r="J1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="27" t="s">
+        <v>850</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="M1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="N1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="O1" s="3" t="s">
         <v>597</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="15.6">
+    <row r="2" spans="1:15" ht="16.2" thickBot="1">
       <c r="A2" s="5" t="s">
         <v>9</v>
       </c>
@@ -3171,20 +3238,23 @@
       <c r="J2" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="K2" s="25" t="s">
+        <v>847</v>
+      </c>
+      <c r="L2" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="L2" s="7" t="s">
+      <c r="M2" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="M2" s="8" t="s">
+      <c r="N2" s="8" t="s">
         <v>747</v>
       </c>
-      <c r="N2" s="8" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" ht="15.6">
+      <c r="O2" s="8" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" ht="16.2" thickBot="1">
       <c r="A3" s="5" t="s">
         <v>18</v>
       </c>
@@ -3213,20 +3283,23 @@
       <c r="J3" s="5" t="s">
         <v>665</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="K3" s="26" t="s">
+        <v>847</v>
+      </c>
+      <c r="L3" s="5" t="s">
         <v>362</v>
       </c>
-      <c r="L3" s="7" t="s">
+      <c r="M3" s="7" t="s">
         <v>711</v>
       </c>
-      <c r="M3" s="8" t="s">
+      <c r="N3" s="8" t="s">
         <v>748</v>
       </c>
-      <c r="N3" s="8" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" ht="15.6">
+      <c r="O3" s="8" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="16.2" thickBot="1">
       <c r="A4" s="5" t="s">
         <v>23</v>
       </c>
@@ -3255,20 +3328,23 @@
       <c r="J4" s="5" t="s">
         <v>666</v>
       </c>
-      <c r="K4" s="5" t="s">
+      <c r="K4" s="26" t="s">
+        <v>847</v>
+      </c>
+      <c r="L4" s="5" t="s">
         <v>708</v>
       </c>
-      <c r="L4" s="7" t="s">
+      <c r="M4" s="7" t="s">
         <v>712</v>
       </c>
-      <c r="M4" s="8" t="s">
+      <c r="N4" s="8" t="s">
         <v>749</v>
       </c>
-      <c r="N4" s="8" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" ht="15.6">
+      <c r="O4" s="8" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="16.2" thickBot="1">
       <c r="A5" s="5" t="s">
         <v>27</v>
       </c>
@@ -3297,20 +3373,23 @@
       <c r="J5" s="5" t="s">
         <v>665</v>
       </c>
-      <c r="K5" s="5" t="s">
+      <c r="K5" s="26" t="s">
+        <v>847</v>
+      </c>
+      <c r="L5" s="5" t="s">
         <v>242</v>
       </c>
-      <c r="L5" s="7" t="s">
+      <c r="M5" s="7" t="s">
         <v>713</v>
       </c>
-      <c r="M5" s="8" t="s">
+      <c r="N5" s="8" t="s">
         <v>750</v>
       </c>
-      <c r="N5" s="8" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" ht="15.6">
+      <c r="O5" s="8" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="16.2" thickBot="1">
       <c r="A6" s="5" t="s">
         <v>31</v>
       </c>
@@ -3339,20 +3418,23 @@
       <c r="J6" s="5" t="s">
         <v>667</v>
       </c>
-      <c r="K6" s="5" t="s">
+      <c r="K6" s="26" t="s">
+        <v>848</v>
+      </c>
+      <c r="L6" s="5" t="s">
         <v>709</v>
       </c>
-      <c r="L6" s="7" t="s">
+      <c r="M6" s="7" t="s">
         <v>714</v>
       </c>
-      <c r="M6" s="8" t="s">
+      <c r="N6" s="8" t="s">
         <v>751</v>
       </c>
-      <c r="N6" s="8" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" ht="15.6">
+      <c r="O6" s="8" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" ht="16.2" thickBot="1">
       <c r="A7" s="5" t="s">
         <v>37</v>
       </c>
@@ -3381,20 +3463,23 @@
       <c r="J7" s="5" t="s">
         <v>668</v>
       </c>
-      <c r="K7" s="10" t="s">
+      <c r="K7" s="26" t="s">
+        <v>849</v>
+      </c>
+      <c r="L7" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="L7" s="7" t="s">
+      <c r="M7" s="7" t="s">
         <v>715</v>
       </c>
-      <c r="M7" s="8" t="s">
+      <c r="N7" s="8" t="s">
         <v>752</v>
       </c>
-      <c r="N7" s="8" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" ht="15.6">
+      <c r="O7" s="8" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" ht="16.2" thickBot="1">
       <c r="A8" s="5" t="s">
         <v>40</v>
       </c>
@@ -3423,20 +3508,23 @@
       <c r="J8" s="10" t="s">
         <v>669</v>
       </c>
-      <c r="K8" s="10" t="s">
+      <c r="K8" s="26" t="s">
+        <v>848</v>
+      </c>
+      <c r="L8" s="10" t="s">
         <v>385</v>
       </c>
-      <c r="L8" s="7" t="s">
+      <c r="M8" s="7" t="s">
         <v>716</v>
       </c>
-      <c r="M8" s="8" t="s">
+      <c r="N8" s="8" t="s">
         <v>753</v>
       </c>
-      <c r="N8" s="8" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" ht="15.6">
+      <c r="O8" s="8" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" ht="16.2" thickBot="1">
       <c r="A9" s="5" t="s">
         <v>43</v>
       </c>
@@ -3465,20 +3553,23 @@
       <c r="J9" s="5" t="s">
         <v>670</v>
       </c>
-      <c r="K9" s="10" t="s">
+      <c r="K9" s="26" t="s">
+        <v>849</v>
+      </c>
+      <c r="L9" s="10" t="s">
         <v>251</v>
       </c>
-      <c r="L9" s="7" t="s">
+      <c r="M9" s="7" t="s">
         <v>717</v>
       </c>
-      <c r="M9" s="8" t="s">
+      <c r="N9" s="8" t="s">
         <v>754</v>
       </c>
-      <c r="N9" s="8" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" ht="15.6">
+      <c r="O9" s="8" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" ht="16.2" thickBot="1">
       <c r="A10" s="5" t="s">
         <v>46</v>
       </c>
@@ -3507,20 +3598,23 @@
       <c r="J10" s="5" t="s">
         <v>671</v>
       </c>
-      <c r="K10" s="10" t="s">
+      <c r="K10" s="26" t="s">
+        <v>849</v>
+      </c>
+      <c r="L10" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="L10" s="7" t="s">
+      <c r="M10" s="7" t="s">
         <v>718</v>
       </c>
-      <c r="M10" s="8" t="s">
+      <c r="N10" s="8" t="s">
         <v>755</v>
       </c>
-      <c r="N10" s="8" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" ht="15.6">
+      <c r="O10" s="8" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" ht="16.2" thickBot="1">
       <c r="A11" s="5" t="s">
         <v>49</v>
       </c>
@@ -3549,20 +3643,23 @@
       <c r="J11" s="5" t="s">
         <v>376</v>
       </c>
-      <c r="K11" s="10" t="s">
+      <c r="K11" s="26" t="s">
+        <v>849</v>
+      </c>
+      <c r="L11" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="L11" s="7" t="s">
+      <c r="M11" s="7" t="s">
         <v>719</v>
       </c>
-      <c r="M11" s="8" t="s">
+      <c r="N11" s="8" t="s">
         <v>756</v>
       </c>
-      <c r="N11" s="8" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" ht="15.6">
+      <c r="O11" s="8" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" ht="16.2" thickBot="1">
       <c r="A12" s="5" t="s">
         <v>52</v>
       </c>
@@ -3591,20 +3688,23 @@
       <c r="J12" s="5" t="s">
         <v>384</v>
       </c>
-      <c r="K12" s="5" t="s">
+      <c r="K12" s="26" t="s">
+        <v>848</v>
+      </c>
+      <c r="L12" s="5" t="s">
         <v>362</v>
       </c>
-      <c r="L12" s="7" t="s">
+      <c r="M12" s="7" t="s">
         <v>720</v>
       </c>
-      <c r="M12" s="8" t="s">
+      <c r="N12" s="8" t="s">
         <v>757</v>
       </c>
-      <c r="N12" s="8" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" ht="15.6">
+      <c r="O12" s="8" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" ht="16.2" thickBot="1">
       <c r="A13" s="5" t="s">
         <v>55</v>
       </c>
@@ -3633,20 +3733,23 @@
       <c r="J13" s="5" t="s">
         <v>672</v>
       </c>
-      <c r="K13" s="10" t="s">
+      <c r="K13" s="26" t="s">
+        <v>848</v>
+      </c>
+      <c r="L13" s="10" t="s">
         <v>710</v>
       </c>
-      <c r="L13" s="7" t="s">
+      <c r="M13" s="7" t="s">
         <v>721</v>
       </c>
-      <c r="M13" s="8" t="s">
+      <c r="N13" s="8" t="s">
         <v>758</v>
       </c>
-      <c r="N13" s="8" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" ht="15.6">
+      <c r="O13" s="8" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" ht="16.2" thickBot="1">
       <c r="A14" s="5" t="s">
         <v>58</v>
       </c>
@@ -3675,20 +3778,23 @@
       <c r="J14" s="5" t="s">
         <v>673</v>
       </c>
-      <c r="K14" s="10" t="s">
+      <c r="K14" s="26" t="s">
+        <v>849</v>
+      </c>
+      <c r="L14" s="10" t="s">
         <v>385</v>
       </c>
-      <c r="L14" s="7" t="s">
+      <c r="M14" s="7" t="s">
         <v>722</v>
       </c>
-      <c r="M14" s="8" t="s">
+      <c r="N14" s="8" t="s">
         <v>759</v>
       </c>
-      <c r="N14" s="8" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" ht="15.6">
+      <c r="O14" s="8" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" ht="16.2" thickBot="1">
       <c r="A15" s="5" t="s">
         <v>61</v>
       </c>
@@ -3717,20 +3823,23 @@
       <c r="J15" s="5" t="s">
         <v>376</v>
       </c>
-      <c r="K15" s="10" t="s">
+      <c r="K15" s="26" t="s">
+        <v>849</v>
+      </c>
+      <c r="L15" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="L15" s="7" t="s">
+      <c r="M15" s="7" t="s">
         <v>723</v>
       </c>
-      <c r="M15" s="8" t="s">
+      <c r="N15" s="8" t="s">
         <v>760</v>
       </c>
-      <c r="N15" s="8" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" ht="15.6">
+      <c r="O15" s="8" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" ht="16.2" thickBot="1">
       <c r="A16" s="5" t="s">
         <v>65</v>
       </c>
@@ -3759,20 +3868,23 @@
       <c r="J16" s="5" t="s">
         <v>369</v>
       </c>
-      <c r="K16" s="5" t="s">
+      <c r="K16" s="26" t="s">
+        <v>848</v>
+      </c>
+      <c r="L16" s="5" t="s">
         <v>362</v>
       </c>
-      <c r="L16" s="7" t="s">
+      <c r="M16" s="7" t="s">
         <v>724</v>
       </c>
-      <c r="M16" s="8" t="s">
+      <c r="N16" s="8" t="s">
         <v>761</v>
       </c>
-      <c r="N16" s="8" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" ht="15.6">
+      <c r="O16" s="8" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" ht="16.2" thickBot="1">
       <c r="A17" s="5" t="s">
         <v>68</v>
       </c>
@@ -3801,20 +3913,23 @@
       <c r="J17" s="5" t="s">
         <v>674</v>
       </c>
-      <c r="K17" s="10" t="s">
+      <c r="K17" s="26" t="s">
+        <v>847</v>
+      </c>
+      <c r="L17" s="10" t="s">
         <v>251</v>
       </c>
-      <c r="L17" s="7" t="s">
+      <c r="M17" s="7" t="s">
         <v>725</v>
       </c>
-      <c r="M17" s="8" t="s">
+      <c r="N17" s="8" t="s">
         <v>762</v>
       </c>
-      <c r="N17" s="8" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" ht="15.6">
+      <c r="O17" s="8" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" ht="16.2" thickBot="1">
       <c r="A18" s="5" t="s">
         <v>71</v>
       </c>
@@ -3843,20 +3958,23 @@
       <c r="J18" s="5" t="s">
         <v>369</v>
       </c>
-      <c r="K18" s="5" t="s">
+      <c r="K18" s="26" t="s">
+        <v>848</v>
+      </c>
+      <c r="L18" s="5" t="s">
         <v>709</v>
       </c>
-      <c r="L18" s="7" t="s">
+      <c r="M18" s="7" t="s">
         <v>726</v>
       </c>
-      <c r="M18" s="8" t="s">
+      <c r="N18" s="8" t="s">
         <v>763</v>
       </c>
-      <c r="N18" s="8" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" ht="15.6">
+      <c r="O18" s="8" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" ht="16.2" thickBot="1">
       <c r="A19" s="5" t="s">
         <v>74</v>
       </c>
@@ -3885,20 +4003,23 @@
       <c r="J19" s="5" t="s">
         <v>675</v>
       </c>
-      <c r="K19" s="10" t="s">
+      <c r="K19" s="26" t="s">
+        <v>849</v>
+      </c>
+      <c r="L19" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="L19" s="7" t="s">
+      <c r="M19" s="7" t="s">
         <v>727</v>
       </c>
-      <c r="M19" s="8" t="s">
+      <c r="N19" s="8" t="s">
         <v>764</v>
       </c>
-      <c r="N19" s="8" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" ht="15.6">
+      <c r="O19" s="8" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" ht="16.2" thickBot="1">
       <c r="A20" s="5" t="s">
         <v>77</v>
       </c>
@@ -3927,20 +4048,23 @@
       <c r="J20" s="10" t="s">
         <v>676</v>
       </c>
-      <c r="K20" s="10" t="s">
+      <c r="K20" s="26" t="s">
+        <v>848</v>
+      </c>
+      <c r="L20" s="10" t="s">
         <v>259</v>
       </c>
-      <c r="L20" s="7" t="s">
+      <c r="M20" s="7" t="s">
         <v>728</v>
       </c>
-      <c r="M20" s="8" t="s">
+      <c r="N20" s="8" t="s">
         <v>765</v>
       </c>
-      <c r="N20" s="8" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" ht="15.6">
+      <c r="O20" s="8" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" ht="16.2" thickBot="1">
       <c r="A21" s="5" t="s">
         <v>80</v>
       </c>
@@ -3969,20 +4093,23 @@
       <c r="J21" s="5" t="s">
         <v>677</v>
       </c>
-      <c r="K21" s="10" t="s">
+      <c r="K21" s="26" t="s">
+        <v>849</v>
+      </c>
+      <c r="L21" s="10" t="s">
         <v>259</v>
       </c>
-      <c r="L21" s="7" t="s">
+      <c r="M21" s="7" t="s">
         <v>729</v>
       </c>
-      <c r="M21" s="8" t="s">
+      <c r="N21" s="8" t="s">
         <v>766</v>
       </c>
-      <c r="N21" s="8" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" ht="15.6">
+      <c r="O21" s="8" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" ht="16.2" thickBot="1">
       <c r="A22" s="5" t="s">
         <v>83</v>
       </c>
@@ -4011,20 +4138,23 @@
       <c r="J22" s="5" t="s">
         <v>678</v>
       </c>
-      <c r="K22" s="10" t="s">
+      <c r="K22" s="26" t="s">
+        <v>849</v>
+      </c>
+      <c r="L22" s="10" t="s">
         <v>251</v>
       </c>
-      <c r="L22" s="7" t="s">
+      <c r="M22" s="7" t="s">
         <v>730</v>
       </c>
-      <c r="M22" s="8" t="s">
+      <c r="N22" s="8" t="s">
         <v>767</v>
       </c>
-      <c r="N22" s="8" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" ht="15.6">
+      <c r="O22" s="8" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" ht="16.2" thickBot="1">
       <c r="A23" s="5" t="s">
         <v>88</v>
       </c>
@@ -4053,20 +4183,23 @@
       <c r="J23" s="5" t="s">
         <v>679</v>
       </c>
-      <c r="K23" s="5" t="s">
+      <c r="K23" s="26" t="s">
+        <v>849</v>
+      </c>
+      <c r="L23" s="5" t="s">
         <v>708</v>
       </c>
-      <c r="L23" s="7" t="s">
+      <c r="M23" s="7" t="s">
         <v>731</v>
       </c>
-      <c r="M23" s="8" t="s">
+      <c r="N23" s="8" t="s">
         <v>768</v>
       </c>
-      <c r="N23" s="8" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" ht="15.6">
+      <c r="O23" s="8" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" ht="16.2" thickBot="1">
       <c r="A24" s="5" t="s">
         <v>91</v>
       </c>
@@ -4095,20 +4228,23 @@
       <c r="J24" s="5" t="s">
         <v>680</v>
       </c>
-      <c r="K24" s="10" t="s">
+      <c r="K24" s="26" t="s">
+        <v>849</v>
+      </c>
+      <c r="L24" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="L24" s="7" t="s">
+      <c r="M24" s="7" t="s">
         <v>732</v>
       </c>
-      <c r="M24" s="8" t="s">
+      <c r="N24" s="8" t="s">
         <v>769</v>
       </c>
-      <c r="N24" s="8" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" ht="15.6">
+      <c r="O24" s="8" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" ht="16.2" thickBot="1">
       <c r="A25" s="5" t="s">
         <v>94</v>
       </c>
@@ -4137,20 +4273,23 @@
       <c r="J25" s="5" t="s">
         <v>681</v>
       </c>
-      <c r="K25" s="10" t="s">
+      <c r="K25" s="26" t="s">
+        <v>849</v>
+      </c>
+      <c r="L25" s="10" t="s">
         <v>259</v>
       </c>
-      <c r="L25" s="7" t="s">
+      <c r="M25" s="7" t="s">
         <v>733</v>
       </c>
-      <c r="M25" s="8" t="s">
+      <c r="N25" s="8" t="s">
         <v>770</v>
       </c>
-      <c r="N25" s="8" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" ht="15.6">
+      <c r="O25" s="8" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" ht="16.2" thickBot="1">
       <c r="A26" s="5" t="s">
         <v>97</v>
       </c>
@@ -4179,20 +4318,23 @@
       <c r="J26" s="5" t="s">
         <v>682</v>
       </c>
-      <c r="K26" s="5" t="s">
+      <c r="K26" s="26" t="s">
+        <v>847</v>
+      </c>
+      <c r="L26" s="5" t="s">
         <v>362</v>
       </c>
-      <c r="L26" s="7" t="s">
+      <c r="M26" s="7" t="s">
         <v>734</v>
       </c>
-      <c r="M26" s="8" t="s">
+      <c r="N26" s="8" t="s">
         <v>771</v>
       </c>
-      <c r="N26" s="8" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" ht="15.6">
+      <c r="O26" s="8" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" ht="16.2" thickBot="1">
       <c r="A27" s="5" t="s">
         <v>600</v>
       </c>
@@ -4221,20 +4363,23 @@
       <c r="J27" s="5" t="s">
         <v>683</v>
       </c>
-      <c r="K27" s="5" t="s">
+      <c r="K27" s="26" t="s">
+        <v>849</v>
+      </c>
+      <c r="L27" s="5" t="s">
         <v>708</v>
       </c>
-      <c r="L27" s="7" t="s">
+      <c r="M27" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="M27" s="8" t="s">
+      <c r="N27" s="8" t="s">
         <v>772</v>
       </c>
-      <c r="N27" s="8" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" ht="15.6">
+      <c r="O27" s="8" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" ht="16.2" thickBot="1">
       <c r="A28" s="5" t="s">
         <v>102</v>
       </c>
@@ -4263,20 +4408,23 @@
       <c r="J28" s="5" t="s">
         <v>684</v>
       </c>
-      <c r="K28" s="5" t="s">
+      <c r="K28" s="26" t="s">
+        <v>849</v>
+      </c>
+      <c r="L28" s="5" t="s">
         <v>259</v>
       </c>
-      <c r="L28" s="7" t="s">
+      <c r="M28" s="7" t="s">
         <v>735</v>
       </c>
-      <c r="M28" s="8" t="s">
+      <c r="N28" s="8" t="s">
         <v>773</v>
       </c>
-      <c r="N28" s="8" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" ht="15.6">
+      <c r="O28" s="8" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" ht="16.2" thickBot="1">
       <c r="A29" s="5" t="s">
         <v>104</v>
       </c>
@@ -4305,20 +4453,23 @@
       <c r="J29" s="5" t="s">
         <v>685</v>
       </c>
-      <c r="K29" s="5" t="s">
+      <c r="K29" s="26" t="s">
+        <v>849</v>
+      </c>
+      <c r="L29" s="5" t="s">
         <v>385</v>
       </c>
-      <c r="L29" s="7" t="s">
+      <c r="M29" s="7" t="s">
         <v>736</v>
       </c>
-      <c r="M29" s="8" t="s">
+      <c r="N29" s="8" t="s">
         <v>774</v>
       </c>
-      <c r="N29" s="8" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" ht="15.6">
+      <c r="O29" s="8" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" ht="16.2" thickBot="1">
       <c r="A30" s="5" t="s">
         <v>106</v>
       </c>
@@ -4347,20 +4498,23 @@
       <c r="J30" s="5" t="s">
         <v>686</v>
       </c>
-      <c r="K30" s="5" t="s">
+      <c r="K30" s="26" t="s">
+        <v>849</v>
+      </c>
+      <c r="L30" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="L30" s="7" t="s">
+      <c r="M30" s="7" t="s">
         <v>737</v>
       </c>
-      <c r="M30" s="8" t="s">
+      <c r="N30" s="8" t="s">
         <v>775</v>
       </c>
-      <c r="N30" s="8" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14" ht="15.6">
+      <c r="O30" s="8" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" ht="16.2" thickBot="1">
       <c r="A31" s="5" t="s">
         <v>109</v>
       </c>
@@ -4389,20 +4543,23 @@
       <c r="J31" s="5" t="s">
         <v>687</v>
       </c>
-      <c r="K31" s="5" t="s">
+      <c r="K31" s="26" t="s">
+        <v>848</v>
+      </c>
+      <c r="L31" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="L31" s="7" t="s">
+      <c r="M31" s="7" t="s">
         <v>738</v>
       </c>
-      <c r="M31" s="8" t="s">
+      <c r="N31" s="8" t="s">
         <v>776</v>
       </c>
-      <c r="N31" s="8" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14" ht="15.6">
+      <c r="O31" s="8" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" ht="16.2" thickBot="1">
       <c r="A32" s="5" t="s">
         <v>112</v>
       </c>
@@ -4431,20 +4588,23 @@
       <c r="J32" s="5" t="s">
         <v>688</v>
       </c>
-      <c r="K32" s="5" t="s">
+      <c r="K32" s="26" t="s">
+        <v>849</v>
+      </c>
+      <c r="L32" s="5" t="s">
         <v>385</v>
       </c>
-      <c r="L32" s="7" t="s">
+      <c r="M32" s="7" t="s">
         <v>739</v>
       </c>
-      <c r="M32" s="8" t="s">
+      <c r="N32" s="8" t="s">
         <v>777</v>
       </c>
-      <c r="N32" s="8" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14" ht="15.6">
+      <c r="O32" s="8" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" ht="16.2" thickBot="1">
       <c r="A33" s="5" t="s">
         <v>116</v>
       </c>
@@ -4473,20 +4633,23 @@
       <c r="J33" s="5" t="s">
         <v>689</v>
       </c>
-      <c r="K33" s="10" t="s">
+      <c r="K33" s="26" t="s">
+        <v>849</v>
+      </c>
+      <c r="L33" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="L33" s="7" t="s">
+      <c r="M33" s="7" t="s">
         <v>740</v>
       </c>
-      <c r="M33" s="8" t="s">
+      <c r="N33" s="8" t="s">
         <v>778</v>
       </c>
-      <c r="N33" s="8" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14" ht="15.6">
+      <c r="O33" s="8" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" ht="16.2" thickBot="1">
       <c r="A34" s="5" t="s">
         <v>119</v>
       </c>
@@ -4515,20 +4678,23 @@
       <c r="J34" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="K34" s="10" t="s">
+      <c r="K34" s="26" t="s">
+        <v>848</v>
+      </c>
+      <c r="L34" s="10" t="s">
         <v>251</v>
       </c>
-      <c r="L34" s="7" t="s">
+      <c r="M34" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="M34" s="8" t="s">
+      <c r="N34" s="8" t="s">
         <v>779</v>
       </c>
-      <c r="N34" s="8" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14" ht="15.6">
+      <c r="O34" s="8" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" ht="16.2" thickBot="1">
       <c r="A35" s="5" t="s">
         <v>127</v>
       </c>
@@ -4557,20 +4723,23 @@
       <c r="J35" s="5" t="s">
         <v>689</v>
       </c>
-      <c r="K35" s="10" t="s">
+      <c r="K35" s="26" t="s">
+        <v>849</v>
+      </c>
+      <c r="L35" s="10" t="s">
         <v>251</v>
       </c>
-      <c r="L35" s="7" t="s">
+      <c r="M35" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="M35" s="8" t="s">
+      <c r="N35" s="8" t="s">
         <v>780</v>
       </c>
-      <c r="N35" s="8" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14" ht="15.6">
+      <c r="O35" s="8" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" ht="16.2" thickBot="1">
       <c r="A36" s="5" t="s">
         <v>134</v>
       </c>
@@ -4599,20 +4768,23 @@
       <c r="J36" s="5" t="s">
         <v>689</v>
       </c>
-      <c r="K36" s="5" t="s">
+      <c r="K36" s="26" t="s">
+        <v>849</v>
+      </c>
+      <c r="L36" s="5" t="s">
         <v>259</v>
       </c>
-      <c r="L36" s="7" t="s">
+      <c r="M36" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="M36" s="8" t="s">
+      <c r="N36" s="8" t="s">
         <v>781</v>
       </c>
-      <c r="N36" s="8" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="37" spans="1:14" ht="15.6">
+      <c r="O36" s="8" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" ht="16.2" thickBot="1">
       <c r="A37" s="5" t="s">
         <v>141</v>
       </c>
@@ -4641,20 +4813,23 @@
       <c r="J37" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="K37" s="5" t="s">
+      <c r="K37" s="26" t="s">
+        <v>849</v>
+      </c>
+      <c r="L37" s="5" t="s">
         <v>259</v>
       </c>
-      <c r="L37" s="7" t="s">
+      <c r="M37" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="M37" s="8" t="s">
+      <c r="N37" s="8" t="s">
         <v>782</v>
       </c>
-      <c r="N37" s="8" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14" ht="15.6">
+      <c r="O37" s="8" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" ht="16.2" thickBot="1">
       <c r="A38" s="5" t="s">
         <v>149</v>
       </c>
@@ -4683,20 +4858,23 @@
       <c r="J38" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="K38" s="5" t="s">
+      <c r="K38" s="26" t="s">
+        <v>849</v>
+      </c>
+      <c r="L38" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="L38" s="7" t="s">
+      <c r="M38" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="M38" s="8" t="s">
+      <c r="N38" s="8" t="s">
         <v>783</v>
       </c>
-      <c r="N38" s="8" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="39" spans="1:14" ht="15.6">
+      <c r="O38" s="8" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" ht="16.2" thickBot="1">
       <c r="A39" s="5" t="s">
         <v>158</v>
       </c>
@@ -4725,20 +4903,23 @@
       <c r="J39" s="5" t="s">
         <v>690</v>
       </c>
-      <c r="K39" s="5" t="s">
+      <c r="K39" s="26" t="s">
+        <v>849</v>
+      </c>
+      <c r="L39" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="L39" s="7" t="s">
+      <c r="M39" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="M39" s="8" t="s">
+      <c r="N39" s="8" t="s">
         <v>784</v>
       </c>
-      <c r="N39" s="8" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="40" spans="1:14" ht="15.6">
+      <c r="O39" s="8" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" ht="16.2" thickBot="1">
       <c r="A40" s="5" t="s">
         <v>165</v>
       </c>
@@ -4767,20 +4948,23 @@
       <c r="J40" s="5" t="s">
         <v>691</v>
       </c>
-      <c r="K40" s="10" t="s">
+      <c r="K40" s="26" t="s">
+        <v>849</v>
+      </c>
+      <c r="L40" s="10" t="s">
         <v>251</v>
       </c>
-      <c r="L40" s="7" t="s">
+      <c r="M40" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="M40" s="8" t="s">
+      <c r="N40" s="8" t="s">
         <v>785</v>
       </c>
-      <c r="N40" s="8" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="41" spans="1:14" ht="15.6">
+      <c r="O40" s="8" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" ht="16.2" thickBot="1">
       <c r="A41" s="5" t="s">
         <v>172</v>
       </c>
@@ -4809,20 +4993,23 @@
       <c r="J41" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="K41" s="5" t="s">
+      <c r="K41" s="26" t="s">
+        <v>848</v>
+      </c>
+      <c r="L41" s="5" t="s">
         <v>259</v>
       </c>
-      <c r="L41" s="7" t="s">
+      <c r="M41" s="7" t="s">
         <v>179</v>
       </c>
-      <c r="M41" s="8" t="s">
+      <c r="N41" s="8" t="s">
         <v>786</v>
       </c>
-      <c r="N41" s="8" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="42" spans="1:14" ht="15.6">
+      <c r="O41" s="8" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" ht="16.2" thickBot="1">
       <c r="A42" s="5" t="s">
         <v>180</v>
       </c>
@@ -4851,20 +5038,23 @@
       <c r="J42" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="K42" s="5" t="s">
+      <c r="K42" s="26" t="s">
+        <v>848</v>
+      </c>
+      <c r="L42" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="L42" s="7" t="s">
+      <c r="M42" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="M42" s="8" t="s">
+      <c r="N42" s="8" t="s">
         <v>787</v>
       </c>
-      <c r="N42" s="8" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="43" spans="1:14" ht="15.6">
+      <c r="O42" s="8" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" ht="16.2" thickBot="1">
       <c r="A43" s="5" t="s">
         <v>189</v>
       </c>
@@ -4893,20 +5083,23 @@
       <c r="J43" s="5" t="s">
         <v>692</v>
       </c>
-      <c r="K43" s="5" t="s">
+      <c r="K43" s="26" t="s">
+        <v>849</v>
+      </c>
+      <c r="L43" s="5" t="s">
         <v>362</v>
       </c>
-      <c r="L43" s="7" t="s">
+      <c r="M43" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="M43" s="8" t="s">
+      <c r="N43" s="8" t="s">
         <v>788</v>
       </c>
-      <c r="N43" s="8" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="44" spans="1:14" ht="15.6">
+      <c r="O43" s="8" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" ht="16.2" thickBot="1">
       <c r="A44" s="5" t="s">
         <v>196</v>
       </c>
@@ -4935,20 +5128,23 @@
       <c r="J44" s="5" t="s">
         <v>693</v>
       </c>
-      <c r="K44" s="5" t="s">
+      <c r="K44" s="26" t="s">
+        <v>849</v>
+      </c>
+      <c r="L44" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="L44" s="7" t="s">
+      <c r="M44" s="7" t="s">
         <v>741</v>
       </c>
-      <c r="M44" s="8" t="s">
+      <c r="N44" s="8" t="s">
         <v>789</v>
       </c>
-      <c r="N44" s="8" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="45" spans="1:14" ht="15.6">
+      <c r="O44" s="8" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" ht="16.2" thickBot="1">
       <c r="A45" s="5" t="s">
         <v>198</v>
       </c>
@@ -4977,20 +5173,23 @@
       <c r="J45" s="5" t="s">
         <v>694</v>
       </c>
-      <c r="K45" s="5" t="s">
+      <c r="K45" s="26" t="s">
+        <v>847</v>
+      </c>
+      <c r="L45" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="L45" s="7" t="s">
+      <c r="M45" s="7" t="s">
         <v>742</v>
       </c>
-      <c r="M45" s="8" t="s">
+      <c r="N45" s="8" t="s">
         <v>790</v>
       </c>
-      <c r="N45" s="8" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="46" spans="1:14" ht="15.6">
+      <c r="O45" s="8" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" ht="16.2" thickBot="1">
       <c r="A46" s="5" t="s">
         <v>201</v>
       </c>
@@ -5019,20 +5218,23 @@
       <c r="J46" s="5" t="s">
         <v>695</v>
       </c>
-      <c r="K46" s="5" t="s">
+      <c r="K46" s="26" t="s">
+        <v>848</v>
+      </c>
+      <c r="L46" s="5" t="s">
         <v>251</v>
       </c>
-      <c r="L46" s="7" t="s">
+      <c r="M46" s="7" t="s">
         <v>743</v>
       </c>
-      <c r="M46" s="8" t="s">
+      <c r="N46" s="8" t="s">
         <v>791</v>
       </c>
-      <c r="N46" s="8" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="47" spans="1:14" ht="15.6">
+      <c r="O46" s="8" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" ht="16.2" thickBot="1">
       <c r="A47" s="5" t="s">
         <v>204</v>
       </c>
@@ -5061,20 +5263,23 @@
       <c r="J47" s="5" t="s">
         <v>696</v>
       </c>
-      <c r="K47" s="5" t="s">
+      <c r="K47" s="26" t="s">
+        <v>848</v>
+      </c>
+      <c r="L47" s="5" t="s">
         <v>259</v>
       </c>
-      <c r="L47" s="7" t="s">
+      <c r="M47" s="7" t="s">
         <v>744</v>
       </c>
-      <c r="M47" s="8" t="s">
+      <c r="N47" s="8" t="s">
         <v>792</v>
       </c>
-      <c r="N47" s="8" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="48" spans="1:14" ht="15.6">
+      <c r="O47" s="8" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" ht="16.2" thickBot="1">
       <c r="A48" s="5" t="s">
         <v>207</v>
       </c>
@@ -5103,20 +5308,23 @@
       <c r="J48" s="5" t="s">
         <v>369</v>
       </c>
-      <c r="K48" s="5" t="s">
+      <c r="K48" s="26" t="s">
+        <v>848</v>
+      </c>
+      <c r="L48" s="5" t="s">
         <v>259</v>
       </c>
-      <c r="L48" s="7" t="s">
+      <c r="M48" s="7" t="s">
         <v>745</v>
       </c>
-      <c r="M48" s="8" t="s">
+      <c r="N48" s="8" t="s">
         <v>793</v>
       </c>
-      <c r="N48" s="8" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="49" spans="1:14" ht="15.6">
+      <c r="O48" s="8" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" ht="16.2" thickBot="1">
       <c r="A49" s="5" t="s">
         <v>210</v>
       </c>
@@ -5145,20 +5353,23 @@
       <c r="J49" s="5" t="s">
         <v>697</v>
       </c>
-      <c r="K49" s="5" t="s">
+      <c r="K49" s="26" t="s">
+        <v>849</v>
+      </c>
+      <c r="L49" s="5" t="s">
         <v>259</v>
       </c>
-      <c r="L49" s="7" t="s">
+      <c r="M49" s="7" t="s">
         <v>746</v>
       </c>
-      <c r="M49" s="8" t="s">
+      <c r="N49" s="8" t="s">
         <v>794</v>
       </c>
-      <c r="N49" s="8" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="50" spans="1:14" ht="15.6">
+      <c r="O49" s="8" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" ht="16.2" thickBot="1">
       <c r="A50" s="5" t="s">
         <v>213</v>
       </c>
@@ -5185,20 +5396,23 @@
         <v>663</v>
       </c>
       <c r="J50" s="5"/>
-      <c r="K50" s="5" t="s">
+      <c r="K50" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="L50" s="5" t="s">
         <v>362</v>
       </c>
-      <c r="L50" s="7" t="s">
+      <c r="M50" s="7" t="s">
         <v>217</v>
       </c>
-      <c r="M50" s="8" t="s">
+      <c r="N50" s="8" t="s">
         <v>795</v>
       </c>
-      <c r="N50" s="8" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="51" spans="1:14" ht="15.6">
+      <c r="O50" s="8" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" ht="16.2" thickBot="1">
       <c r="A51" s="5" t="s">
         <v>218</v>
       </c>
@@ -5227,20 +5441,23 @@
       <c r="J51" s="5" t="s">
         <v>224</v>
       </c>
-      <c r="K51" s="5" t="s">
+      <c r="K51" s="26" t="s">
+        <v>848</v>
+      </c>
+      <c r="L51" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="L51" s="7" t="s">
+      <c r="M51" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="M51" s="8" t="s">
+      <c r="N51" s="8" t="s">
         <v>796</v>
       </c>
-      <c r="N51" s="8" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="52" spans="1:14" ht="15.6">
+      <c r="O51" s="8" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" ht="16.2" thickBot="1">
       <c r="A52" s="5" t="s">
         <v>226</v>
       </c>
@@ -5269,20 +5486,23 @@
       <c r="J52" s="5" t="s">
         <v>232</v>
       </c>
-      <c r="K52" s="5" t="s">
+      <c r="K52" s="26" t="s">
+        <v>849</v>
+      </c>
+      <c r="L52" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="L52" s="7" t="s">
+      <c r="M52" s="7" t="s">
         <v>234</v>
       </c>
-      <c r="M52" s="8" t="s">
+      <c r="N52" s="8" t="s">
         <v>797</v>
       </c>
-      <c r="N52" s="8" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="53" spans="1:14" ht="15.6">
+      <c r="O52" s="8" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" ht="16.2" thickBot="1">
       <c r="A53" s="5" t="s">
         <v>235</v>
       </c>
@@ -5311,20 +5531,23 @@
       <c r="J53" s="5" t="s">
         <v>241</v>
       </c>
-      <c r="K53" s="5" t="s">
+      <c r="K53" s="26" t="s">
+        <v>849</v>
+      </c>
+      <c r="L53" s="5" t="s">
         <v>242</v>
       </c>
-      <c r="L53" s="7" t="s">
+      <c r="M53" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="M53" s="8" t="s">
+      <c r="N53" s="8" t="s">
         <v>798</v>
       </c>
-      <c r="N53" s="8" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="54" spans="1:14" ht="15.6">
+      <c r="O53" s="8" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" ht="16.2" thickBot="1">
       <c r="A54" s="5" t="s">
         <v>244</v>
       </c>
@@ -5353,20 +5576,23 @@
       <c r="J54" s="5" t="s">
         <v>250</v>
       </c>
-      <c r="K54" s="5" t="s">
+      <c r="K54" s="26" t="s">
+        <v>848</v>
+      </c>
+      <c r="L54" s="5" t="s">
         <v>251</v>
       </c>
-      <c r="L54" s="7" t="s">
+      <c r="M54" s="7" t="s">
         <v>252</v>
       </c>
-      <c r="M54" s="8" t="s">
+      <c r="N54" s="8" t="s">
         <v>799</v>
       </c>
-      <c r="N54" s="8" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="55" spans="1:14" ht="15.6">
+      <c r="O54" s="8" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15" ht="16.2" thickBot="1">
       <c r="A55" s="5" t="s">
         <v>253</v>
       </c>
@@ -5393,20 +5619,23 @@
         <v>258</v>
       </c>
       <c r="J55" s="5"/>
-      <c r="K55" s="5" t="s">
+      <c r="K55" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="L55" s="5" t="s">
         <v>259</v>
       </c>
-      <c r="L55" s="7" t="s">
+      <c r="M55" s="7" t="s">
         <v>260</v>
       </c>
-      <c r="M55" s="8" t="s">
+      <c r="N55" s="8" t="s">
         <v>800</v>
       </c>
-      <c r="N55" s="8" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="56" spans="1:14" ht="15.6">
+      <c r="O55" s="8" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15" ht="16.2" thickBot="1">
       <c r="A56" s="5" t="s">
         <v>261</v>
       </c>
@@ -5435,20 +5664,23 @@
       <c r="J56" s="5" t="s">
         <v>267</v>
       </c>
-      <c r="K56" s="5" t="s">
+      <c r="K56" s="26" t="s">
+        <v>849</v>
+      </c>
+      <c r="L56" s="5" t="s">
         <v>259</v>
       </c>
-      <c r="L56" s="7" t="s">
+      <c r="M56" s="7" t="s">
         <v>268</v>
       </c>
-      <c r="M56" s="8" t="s">
+      <c r="N56" s="8" t="s">
         <v>801</v>
       </c>
-      <c r="N56" s="8" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="57" spans="1:14" ht="15.6">
+      <c r="O56" s="8" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15" ht="16.2" thickBot="1">
       <c r="A57" s="5" t="s">
         <v>269</v>
       </c>
@@ -5475,20 +5707,23 @@
       <c r="J57" s="5" t="s">
         <v>274</v>
       </c>
-      <c r="K57" s="5" t="s">
+      <c r="K57" s="26" t="s">
+        <v>847</v>
+      </c>
+      <c r="L57" s="5" t="s">
         <v>251</v>
       </c>
-      <c r="L57" s="7" t="s">
+      <c r="M57" s="7" t="s">
         <v>275</v>
       </c>
-      <c r="M57" s="8" t="s">
+      <c r="N57" s="8" t="s">
         <v>601</v>
       </c>
-      <c r="N57" s="8" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="58" spans="1:14" ht="15.6">
+      <c r="O57" s="8" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" ht="16.2" thickBot="1">
       <c r="A58" s="5" t="s">
         <v>276</v>
       </c>
@@ -5517,20 +5752,23 @@
       <c r="J58" s="5" t="s">
         <v>282</v>
       </c>
-      <c r="K58" s="5" t="s">
+      <c r="K58" s="26" t="s">
+        <v>848</v>
+      </c>
+      <c r="L58" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="L58" s="7" t="s">
+      <c r="M58" s="7" t="s">
         <v>283</v>
       </c>
-      <c r="M58" s="8" t="s">
+      <c r="N58" s="8" t="s">
         <v>802</v>
       </c>
-      <c r="N58" s="8" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="59" spans="1:14" ht="15.6">
+      <c r="O58" s="8" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" ht="16.2" thickBot="1">
       <c r="A59" s="5" t="s">
         <v>284</v>
       </c>
@@ -5559,20 +5797,23 @@
       <c r="J59" s="5" t="s">
         <v>282</v>
       </c>
-      <c r="K59" s="5" t="s">
+      <c r="K59" s="26" t="s">
+        <v>848</v>
+      </c>
+      <c r="L59" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="L59" s="7" t="s">
+      <c r="M59" s="7" t="s">
         <v>290</v>
       </c>
-      <c r="M59" s="8" t="s">
+      <c r="N59" s="8" t="s">
         <v>803</v>
       </c>
-      <c r="N59" s="8" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="60" spans="1:14" ht="15.6">
+      <c r="O59" s="8" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15" ht="16.2" thickBot="1">
       <c r="A60" s="5" t="s">
         <v>291</v>
       </c>
@@ -5597,20 +5838,23 @@
         <v>295</v>
       </c>
       <c r="J60" s="5"/>
-      <c r="K60" s="5" t="s">
+      <c r="K60" s="26" t="s">
+        <v>848</v>
+      </c>
+      <c r="L60" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="L60" s="7" t="s">
+      <c r="M60" s="7" t="s">
         <v>296</v>
       </c>
-      <c r="M60" s="8" t="s">
+      <c r="N60" s="8" t="s">
         <v>804</v>
       </c>
-      <c r="N60" s="8" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="61" spans="1:14" ht="15.6">
+      <c r="O60" s="8" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" ht="16.2" thickBot="1">
       <c r="A61" s="5" t="s">
         <v>297</v>
       </c>
@@ -5637,20 +5881,23 @@
       <c r="J61" s="5" t="s">
         <v>302</v>
       </c>
-      <c r="K61" s="5" t="s">
+      <c r="K61" s="26" t="s">
+        <v>849</v>
+      </c>
+      <c r="L61" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="L61" s="7" t="s">
+      <c r="M61" s="7" t="s">
         <v>303</v>
       </c>
-      <c r="M61" s="8" t="s">
+      <c r="N61" s="8" t="s">
         <v>805</v>
       </c>
-      <c r="N61" s="8" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="62" spans="1:14" ht="15.6">
+      <c r="O61" s="8" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15" ht="16.2" thickBot="1">
       <c r="A62" s="5" t="s">
         <v>304</v>
       </c>
@@ -5677,20 +5924,23 @@
       <c r="J62" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="K62" s="5" t="s">
+      <c r="K62" s="26" t="s">
+        <v>849</v>
+      </c>
+      <c r="L62" s="5" t="s">
         <v>259</v>
       </c>
-      <c r="L62" s="7" t="s">
+      <c r="M62" s="7" t="s">
         <v>310</v>
       </c>
-      <c r="M62" s="8" t="s">
+      <c r="N62" s="8" t="s">
         <v>806</v>
       </c>
-      <c r="N62" s="8" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="63" spans="1:14" ht="15.6">
+      <c r="O62" s="8" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" ht="16.2" thickBot="1">
       <c r="A63" s="5" t="s">
         <v>311</v>
       </c>
@@ -5719,20 +5969,23 @@
       <c r="J63" s="5" t="s">
         <v>317</v>
       </c>
-      <c r="K63" s="5" t="s">
+      <c r="K63" s="26" t="s">
+        <v>848</v>
+      </c>
+      <c r="L63" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="L63" s="7" t="s">
+      <c r="M63" s="7" t="s">
         <v>318</v>
       </c>
-      <c r="M63" s="8" t="s">
+      <c r="N63" s="8" t="s">
         <v>807</v>
       </c>
-      <c r="N63" s="8" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="64" spans="1:14" ht="15.6">
+      <c r="O63" s="8" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" ht="16.2" thickBot="1">
       <c r="A64" s="5" t="s">
         <v>319</v>
       </c>
@@ -5759,20 +6012,23 @@
       <c r="J64" s="10" t="s">
         <v>324</v>
       </c>
-      <c r="K64" s="5" t="s">
+      <c r="K64" s="26" t="s">
+        <v>848</v>
+      </c>
+      <c r="L64" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="L64" s="7" t="s">
+      <c r="M64" s="7" t="s">
         <v>325</v>
       </c>
-      <c r="M64" s="8" t="s">
+      <c r="N64" s="8" t="s">
         <v>808</v>
       </c>
-      <c r="N64" s="8" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="65" spans="1:14" ht="15.6">
+      <c r="O64" s="8" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15" ht="16.2" thickBot="1">
       <c r="A65" s="5" t="s">
         <v>326</v>
       </c>
@@ -5799,20 +6055,23 @@
         <v>331</v>
       </c>
       <c r="J65" s="5"/>
-      <c r="K65" s="5" t="s">
+      <c r="K65" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="L65" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="L65" s="7" t="s">
+      <c r="M65" s="7" t="s">
         <v>332</v>
       </c>
-      <c r="M65" s="8" t="s">
+      <c r="N65" s="8" t="s">
         <v>809</v>
       </c>
-      <c r="N65" s="8" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="66" spans="1:14" ht="15.6">
+      <c r="O65" s="8" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15" ht="16.2" thickBot="1">
       <c r="A66" s="5" t="s">
         <v>333</v>
       </c>
@@ -5839,20 +6098,23 @@
         <v>338</v>
       </c>
       <c r="J66" s="5"/>
-      <c r="K66" s="5" t="s">
+      <c r="K66" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="L66" s="5" t="s">
         <v>259</v>
       </c>
-      <c r="L66" s="7" t="s">
+      <c r="M66" s="7" t="s">
         <v>339</v>
       </c>
-      <c r="M66" s="8" t="s">
+      <c r="N66" s="8" t="s">
         <v>810</v>
       </c>
-      <c r="N66" s="8" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="67" spans="1:14" ht="15.6">
+      <c r="O66" s="8" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15" ht="16.2" thickBot="1">
       <c r="A67" s="5" t="s">
         <v>340</v>
       </c>
@@ -5881,20 +6143,23 @@
       <c r="J67" s="5" t="s">
         <v>346</v>
       </c>
-      <c r="K67" s="5" t="s">
+      <c r="K67" s="26" t="s">
+        <v>847</v>
+      </c>
+      <c r="L67" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="L67" s="7" t="s">
+      <c r="M67" s="7" t="s">
         <v>347</v>
       </c>
-      <c r="M67" s="8" t="s">
+      <c r="N67" s="8" t="s">
         <v>811</v>
       </c>
-      <c r="N67" s="8" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="68" spans="1:14" ht="15.6">
+      <c r="O67" s="8" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15" ht="16.2" thickBot="1">
       <c r="A68" s="5" t="s">
         <v>348</v>
       </c>
@@ -5921,20 +6186,23 @@
       <c r="J68" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="K68" s="5" t="s">
+      <c r="K68" s="26" t="s">
+        <v>849</v>
+      </c>
+      <c r="L68" s="5" t="s">
         <v>259</v>
       </c>
-      <c r="L68" s="7" t="s">
+      <c r="M68" s="7" t="s">
         <v>354</v>
       </c>
-      <c r="M68" s="8" t="s">
+      <c r="N68" s="8" t="s">
         <v>812</v>
       </c>
-      <c r="N68" s="8" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="69" spans="1:14" ht="15.6">
+      <c r="O68" s="8" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15" ht="16.2" thickBot="1">
       <c r="A69" s="5" t="s">
         <v>355</v>
       </c>
@@ -5963,20 +6231,23 @@
       <c r="J69" s="5" t="s">
         <v>361</v>
       </c>
-      <c r="K69" s="5" t="s">
+      <c r="K69" s="26" t="s">
+        <v>849</v>
+      </c>
+      <c r="L69" s="5" t="s">
         <v>362</v>
       </c>
-      <c r="L69" s="7" t="s">
+      <c r="M69" s="7" t="s">
         <v>363</v>
       </c>
-      <c r="M69" s="8" t="s">
+      <c r="N69" s="8" t="s">
         <v>813</v>
       </c>
-      <c r="N69" s="8" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="70" spans="1:14" ht="15.6">
+      <c r="O69" s="8" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15" ht="16.2" thickBot="1">
       <c r="A70" s="5" t="s">
         <v>364</v>
       </c>
@@ -6003,20 +6274,23 @@
       <c r="J70" s="5" t="s">
         <v>369</v>
       </c>
-      <c r="K70" s="5" t="s">
+      <c r="K70" s="26" t="s">
+        <v>848</v>
+      </c>
+      <c r="L70" s="5" t="s">
         <v>362</v>
       </c>
-      <c r="L70" s="7" t="s">
+      <c r="M70" s="7" t="s">
         <v>370</v>
       </c>
-      <c r="M70" s="8" t="s">
+      <c r="N70" s="8" t="s">
         <v>814</v>
       </c>
-      <c r="N70" s="8" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="71" spans="1:14" ht="15.6">
+      <c r="O70" s="8" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15" ht="16.2" thickBot="1">
       <c r="A71" s="5" t="s">
         <v>371</v>
       </c>
@@ -6045,20 +6319,23 @@
       <c r="J71" s="5" t="s">
         <v>376</v>
       </c>
-      <c r="K71" s="5" t="s">
+      <c r="K71" s="26" t="s">
+        <v>849</v>
+      </c>
+      <c r="L71" s="5" t="s">
         <v>259</v>
       </c>
-      <c r="L71" s="7" t="s">
+      <c r="M71" s="7" t="s">
         <v>377</v>
       </c>
-      <c r="M71" s="8" t="s">
+      <c r="N71" s="8" t="s">
         <v>815</v>
       </c>
-      <c r="N71" s="8" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="72" spans="1:14" ht="15.6">
+      <c r="O71" s="8" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="72" spans="1:15" ht="16.2" thickBot="1">
       <c r="A72" s="5" t="s">
         <v>378</v>
       </c>
@@ -6087,20 +6364,23 @@
       <c r="J72" s="5" t="s">
         <v>384</v>
       </c>
-      <c r="K72" s="5" t="s">
+      <c r="K72" s="26" t="s">
+        <v>848</v>
+      </c>
+      <c r="L72" s="5" t="s">
         <v>385</v>
       </c>
-      <c r="L72" s="7" t="s">
+      <c r="M72" s="7" t="s">
         <v>386</v>
       </c>
-      <c r="M72" s="8" t="s">
+      <c r="N72" s="8" t="s">
         <v>816</v>
       </c>
-      <c r="N72" s="8" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="73" spans="1:14" ht="15.6">
+      <c r="O72" s="8" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="73" spans="1:15" ht="16.2" thickBot="1">
       <c r="A73" s="5" t="s">
         <v>387</v>
       </c>
@@ -6129,20 +6409,23 @@
       <c r="J73" s="5" t="s">
         <v>698</v>
       </c>
-      <c r="K73" s="5" t="s">
+      <c r="K73" s="26" t="s">
+        <v>848</v>
+      </c>
+      <c r="L73" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="L73" s="7" t="s">
+      <c r="M73" s="7" t="s">
         <v>393</v>
       </c>
-      <c r="M73" s="8" t="s">
+      <c r="N73" s="8" t="s">
         <v>817</v>
       </c>
-      <c r="N73" s="8" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="74" spans="1:14" ht="15.6">
+      <c r="O73" s="8" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15" ht="16.2" thickBot="1">
       <c r="A74" s="5" t="s">
         <v>394</v>
       </c>
@@ -6171,20 +6454,23 @@
       <c r="J74" s="5" t="s">
         <v>699</v>
       </c>
-      <c r="K74" s="5" t="s">
+      <c r="K74" s="26" t="s">
+        <v>848</v>
+      </c>
+      <c r="L74" s="5" t="s">
         <v>259</v>
       </c>
-      <c r="L74" s="7" t="s">
+      <c r="M74" s="7" t="s">
         <v>400</v>
       </c>
-      <c r="M74" s="8" t="s">
+      <c r="N74" s="8" t="s">
         <v>818</v>
       </c>
-      <c r="N74" s="8" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="75" spans="1:14" ht="15.6">
+      <c r="O74" s="8" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="75" spans="1:15" ht="16.2" thickBot="1">
       <c r="A75" s="5" t="s">
         <v>401</v>
       </c>
@@ -6213,20 +6499,23 @@
       <c r="J75" s="5" t="s">
         <v>700</v>
       </c>
-      <c r="K75" s="10" t="s">
+      <c r="K75" s="26" t="s">
+        <v>848</v>
+      </c>
+      <c r="L75" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="L75" s="7" t="s">
+      <c r="M75" s="7" t="s">
         <v>407</v>
       </c>
-      <c r="M75" s="8" t="s">
+      <c r="N75" s="8" t="s">
         <v>819</v>
       </c>
-      <c r="N75" s="8" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="76" spans="1:14" ht="15.6">
+      <c r="O75" s="8" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15" ht="16.2" thickBot="1">
       <c r="A76" s="5" t="s">
         <v>408</v>
       </c>
@@ -6255,20 +6544,23 @@
       <c r="J76" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="K76" s="10" t="s">
+      <c r="K76" s="26" t="s">
+        <v>848</v>
+      </c>
+      <c r="L76" s="10" t="s">
         <v>385</v>
       </c>
-      <c r="L76" s="7" t="s">
+      <c r="M76" s="7" t="s">
         <v>414</v>
       </c>
-      <c r="M76" s="8" t="s">
+      <c r="N76" s="8" t="s">
         <v>820</v>
       </c>
-      <c r="N76" s="8" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="77" spans="1:14" ht="15.6">
+      <c r="O76" s="8" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="77" spans="1:15" ht="16.2" thickBot="1">
       <c r="A77" s="5" t="s">
         <v>415</v>
       </c>
@@ -6297,20 +6589,23 @@
       <c r="J77" s="5" t="s">
         <v>421</v>
       </c>
-      <c r="K77" s="5" t="s">
+      <c r="K77" s="26" t="s">
+        <v>849</v>
+      </c>
+      <c r="L77" s="5" t="s">
         <v>422</v>
       </c>
-      <c r="L77" s="7" t="s">
+      <c r="M77" s="7" t="s">
         <v>423</v>
       </c>
-      <c r="M77" s="8" t="s">
+      <c r="N77" s="8" t="s">
         <v>821</v>
       </c>
-      <c r="N77" s="8" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="78" spans="1:14" ht="15.6">
+      <c r="O77" s="8" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="78" spans="1:15" ht="16.2" thickBot="1">
       <c r="A78" s="5" t="s">
         <v>424</v>
       </c>
@@ -6339,20 +6634,23 @@
       <c r="J78" s="5" t="s">
         <v>430</v>
       </c>
-      <c r="K78" s="10" t="s">
+      <c r="K78" s="26" t="s">
+        <v>849</v>
+      </c>
+      <c r="L78" s="10" t="s">
         <v>385</v>
       </c>
-      <c r="L78" s="7" t="s">
+      <c r="M78" s="7" t="s">
         <v>431</v>
       </c>
-      <c r="M78" s="8" t="s">
+      <c r="N78" s="8" t="s">
         <v>822</v>
       </c>
-      <c r="N78" s="8" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="79" spans="1:14" ht="15.6">
+      <c r="O78" s="8" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15" ht="16.2" thickBot="1">
       <c r="A79" s="5" t="s">
         <v>432</v>
       </c>
@@ -6381,20 +6679,23 @@
       <c r="J79" s="5" t="s">
         <v>438</v>
       </c>
-      <c r="K79" s="5" t="s">
+      <c r="K79" s="26" t="s">
+        <v>848</v>
+      </c>
+      <c r="L79" s="5" t="s">
         <v>709</v>
       </c>
-      <c r="L79" s="7" t="s">
+      <c r="M79" s="7" t="s">
         <v>439</v>
       </c>
-      <c r="M79" s="8" t="s">
+      <c r="N79" s="8" t="s">
         <v>823</v>
       </c>
-      <c r="N79" s="8" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="80" spans="1:14" ht="15.6">
+      <c r="O79" s="8" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="80" spans="1:15" ht="16.2" thickBot="1">
       <c r="A80" s="5" t="s">
         <v>440</v>
       </c>
@@ -6423,20 +6724,23 @@
       <c r="J80" s="5" t="s">
         <v>446</v>
       </c>
-      <c r="K80" s="10" t="s">
+      <c r="K80" s="26" t="s">
+        <v>848</v>
+      </c>
+      <c r="L80" s="10" t="s">
         <v>385</v>
       </c>
-      <c r="L80" s="7" t="s">
+      <c r="M80" s="7" t="s">
         <v>447</v>
       </c>
-      <c r="M80" s="8" t="s">
+      <c r="N80" s="8" t="s">
         <v>824</v>
       </c>
-      <c r="N80" s="8" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="81" spans="1:14" ht="15.6">
+      <c r="O80" s="8" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="81" spans="1:15" ht="16.2" thickBot="1">
       <c r="A81" s="5" t="s">
         <v>448</v>
       </c>
@@ -6465,20 +6769,23 @@
       <c r="J81" s="5" t="s">
         <v>438</v>
       </c>
-      <c r="K81" s="5" t="s">
+      <c r="K81" s="26" t="s">
+        <v>848</v>
+      </c>
+      <c r="L81" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="L81" s="7" t="s">
+      <c r="M81" s="7" t="s">
         <v>453</v>
       </c>
-      <c r="M81" s="8" t="s">
+      <c r="N81" s="8" t="s">
         <v>825</v>
       </c>
-      <c r="N81" s="8" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="82" spans="1:14" ht="15.6">
+      <c r="O81" s="8" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="82" spans="1:15" ht="16.2" thickBot="1">
       <c r="A82" s="5" t="s">
         <v>454</v>
       </c>
@@ -6507,20 +6814,23 @@
       <c r="J82" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="K82" s="5" t="s">
+      <c r="K82" s="26" t="s">
+        <v>849</v>
+      </c>
+      <c r="L82" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="L82" s="7" t="s">
+      <c r="M82" s="7" t="s">
         <v>460</v>
       </c>
-      <c r="M82" s="8" t="s">
+      <c r="N82" s="8" t="s">
         <v>826</v>
       </c>
-      <c r="N82" s="8" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="83" spans="1:14" ht="15.6">
+      <c r="O82" s="8" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="83" spans="1:15" ht="16.2" thickBot="1">
       <c r="A83" s="5" t="s">
         <v>461</v>
       </c>
@@ -6549,20 +6859,23 @@
       <c r="J83" s="5" t="s">
         <v>446</v>
       </c>
-      <c r="K83" s="10" t="s">
+      <c r="K83" s="26" t="s">
+        <v>848</v>
+      </c>
+      <c r="L83" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="L83" s="7" t="s">
+      <c r="M83" s="7" t="s">
         <v>467</v>
       </c>
-      <c r="M83" s="8" t="s">
+      <c r="N83" s="8" t="s">
         <v>827</v>
       </c>
-      <c r="N83" s="8" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="84" spans="1:14" ht="15.6">
+      <c r="O83" s="8" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="84" spans="1:15" ht="16.2" thickBot="1">
       <c r="A84" s="5" t="s">
         <v>468</v>
       </c>
@@ -6591,20 +6904,23 @@
       <c r="J84" s="5" t="s">
         <v>474</v>
       </c>
-      <c r="K84" s="5" t="s">
+      <c r="K84" s="26" t="s">
+        <v>849</v>
+      </c>
+      <c r="L84" s="5" t="s">
         <v>709</v>
       </c>
-      <c r="L84" s="7" t="s">
+      <c r="M84" s="7" t="s">
         <v>475</v>
       </c>
-      <c r="M84" s="8" t="s">
+      <c r="N84" s="8" t="s">
         <v>828</v>
       </c>
-      <c r="N84" s="8" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="85" spans="1:14" ht="15.6">
+      <c r="O84" s="8" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="85" spans="1:15" ht="16.2" thickBot="1">
       <c r="A85" s="5" t="s">
         <v>476</v>
       </c>
@@ -6633,20 +6949,23 @@
       <c r="J85" s="5" t="s">
         <v>701</v>
       </c>
-      <c r="K85" s="5" t="s">
+      <c r="K85" s="26" t="s">
+        <v>849</v>
+      </c>
+      <c r="L85" s="5" t="s">
         <v>482</v>
       </c>
-      <c r="L85" s="7" t="s">
+      <c r="M85" s="7" t="s">
         <v>483</v>
       </c>
-      <c r="M85" s="8" t="s">
+      <c r="N85" s="8" t="s">
         <v>829</v>
       </c>
-      <c r="N85" s="8" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="86" spans="1:14" ht="15.6">
+      <c r="O85" s="8" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="86" spans="1:15" ht="16.2" thickBot="1">
       <c r="A86" s="5" t="s">
         <v>484</v>
       </c>
@@ -6675,20 +6994,23 @@
       <c r="J86" s="5" t="s">
         <v>702</v>
       </c>
-      <c r="K86" s="5" t="s">
+      <c r="K86" s="26" t="s">
+        <v>849</v>
+      </c>
+      <c r="L86" s="5" t="s">
         <v>259</v>
       </c>
-      <c r="L86" s="7" t="s">
+      <c r="M86" s="7" t="s">
         <v>490</v>
       </c>
-      <c r="M86" s="8" t="s">
+      <c r="N86" s="8" t="s">
         <v>830</v>
       </c>
-      <c r="N86" s="8" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="87" spans="1:14" ht="15.6">
+      <c r="O86" s="8" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="87" spans="1:15" ht="16.2" thickBot="1">
       <c r="A87" s="5" t="s">
         <v>491</v>
       </c>
@@ -6717,20 +7039,23 @@
       <c r="J87" s="5" t="s">
         <v>703</v>
       </c>
-      <c r="K87" s="10" t="s">
+      <c r="K87" s="26" t="s">
+        <v>849</v>
+      </c>
+      <c r="L87" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="L87" s="7" t="s">
+      <c r="M87" s="7" t="s">
         <v>497</v>
       </c>
-      <c r="M87" s="8" t="s">
+      <c r="N87" s="8" t="s">
         <v>831</v>
       </c>
-      <c r="N87" s="8" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="88" spans="1:14" ht="15.6">
+      <c r="O87" s="8" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="88" spans="1:15" ht="16.2" thickBot="1">
       <c r="A88" s="5" t="s">
         <v>498</v>
       </c>
@@ -6759,20 +7084,23 @@
       <c r="J88" s="5" t="s">
         <v>504</v>
       </c>
-      <c r="K88" s="5" t="s">
+      <c r="K88" s="26" t="s">
+        <v>847</v>
+      </c>
+      <c r="L88" s="5" t="s">
         <v>251</v>
       </c>
-      <c r="L88" s="7" t="s">
+      <c r="M88" s="7" t="s">
         <v>505</v>
       </c>
-      <c r="M88" s="8" t="s">
+      <c r="N88" s="8" t="s">
         <v>832</v>
       </c>
-      <c r="N88" s="8" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="89" spans="1:14" ht="15.6">
+      <c r="O88" s="8" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="89" spans="1:15" ht="16.2" thickBot="1">
       <c r="A89" s="5" t="s">
         <v>506</v>
       </c>
@@ -6801,20 +7129,23 @@
       <c r="J89" s="5" t="s">
         <v>512</v>
       </c>
-      <c r="K89" s="5" t="s">
+      <c r="K89" s="26" t="s">
+        <v>848</v>
+      </c>
+      <c r="L89" s="5" t="s">
         <v>362</v>
       </c>
-      <c r="L89" s="7" t="s">
+      <c r="M89" s="7" t="s">
         <v>513</v>
       </c>
-      <c r="M89" s="8" t="s">
+      <c r="N89" s="8" t="s">
         <v>833</v>
       </c>
-      <c r="N89" s="8" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="90" spans="1:14" ht="15.6">
+      <c r="O89" s="8" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="90" spans="1:15" ht="16.2" thickBot="1">
       <c r="A90" s="5" t="s">
         <v>514</v>
       </c>
@@ -6843,20 +7174,23 @@
       <c r="J90" s="5" t="s">
         <v>699</v>
       </c>
-      <c r="K90" s="5" t="s">
+      <c r="K90" s="26" t="s">
+        <v>848</v>
+      </c>
+      <c r="L90" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="L90" s="7" t="s">
+      <c r="M90" s="7" t="s">
         <v>520</v>
       </c>
-      <c r="M90" s="8" t="s">
+      <c r="N90" s="8" t="s">
         <v>834</v>
       </c>
-      <c r="N90" s="8" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="91" spans="1:14" ht="15.6">
+      <c r="O90" s="8" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="91" spans="1:15" ht="16.2" thickBot="1">
       <c r="A91" s="5" t="s">
         <v>521</v>
       </c>
@@ -6885,20 +7219,23 @@
       <c r="J91" s="5" t="s">
         <v>421</v>
       </c>
-      <c r="K91" s="5" t="s">
+      <c r="K91" s="26" t="s">
+        <v>849</v>
+      </c>
+      <c r="L91" s="5" t="s">
         <v>259</v>
       </c>
-      <c r="L91" s="7" t="s">
+      <c r="M91" s="7" t="s">
         <v>527</v>
       </c>
-      <c r="M91" s="8" t="s">
+      <c r="N91" s="8" t="s">
         <v>835</v>
       </c>
-      <c r="N91" s="8" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="92" spans="1:14" ht="15.6">
+      <c r="O91" s="8" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="92" spans="1:15" ht="16.2" thickBot="1">
       <c r="A92" s="5" t="s">
         <v>528</v>
       </c>
@@ -6927,20 +7264,23 @@
       <c r="J92" s="5" t="s">
         <v>703</v>
       </c>
-      <c r="K92" s="5" t="s">
+      <c r="K92" s="26" t="s">
+        <v>849</v>
+      </c>
+      <c r="L92" s="5" t="s">
         <v>259</v>
       </c>
-      <c r="L92" s="7" t="s">
+      <c r="M92" s="7" t="s">
         <v>534</v>
       </c>
-      <c r="M92" s="8" t="s">
+      <c r="N92" s="8" t="s">
         <v>836</v>
       </c>
-      <c r="N92" s="8" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="93" spans="1:14" ht="15.6">
+      <c r="O92" s="8" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="93" spans="1:15" ht="16.2" thickBot="1">
       <c r="A93" s="5" t="s">
         <v>535</v>
       </c>
@@ -6969,20 +7309,23 @@
       <c r="J93" s="5" t="s">
         <v>541</v>
       </c>
-      <c r="K93" s="5" t="s">
+      <c r="K93" s="26" t="s">
+        <v>847</v>
+      </c>
+      <c r="L93" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="L93" s="7" t="s">
+      <c r="M93" s="7" t="s">
         <v>542</v>
       </c>
-      <c r="M93" s="8" t="s">
+      <c r="N93" s="8" t="s">
         <v>837</v>
       </c>
-      <c r="N93" s="8" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="94" spans="1:14" ht="15.6">
+      <c r="O93" s="8" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="94" spans="1:15" ht="16.2" thickBot="1">
       <c r="A94" s="5" t="s">
         <v>543</v>
       </c>
@@ -7011,20 +7354,23 @@
       <c r="J94" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="K94" s="5" t="s">
+      <c r="K94" s="26" t="s">
+        <v>849</v>
+      </c>
+      <c r="L94" s="5" t="s">
         <v>259</v>
       </c>
-      <c r="L94" s="7" t="s">
+      <c r="M94" s="7" t="s">
         <v>548</v>
       </c>
-      <c r="M94" s="8" t="s">
+      <c r="N94" s="8" t="s">
         <v>838</v>
       </c>
-      <c r="N94" s="8" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="95" spans="1:14" ht="15.6">
+      <c r="O94" s="8" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="95" spans="1:15" ht="16.2" thickBot="1">
       <c r="A95" s="5" t="s">
         <v>549</v>
       </c>
@@ -7053,20 +7399,23 @@
       <c r="J95" s="5" t="s">
         <v>555</v>
       </c>
-      <c r="K95" s="10" t="s">
+      <c r="K95" s="26" t="s">
+        <v>849</v>
+      </c>
+      <c r="L95" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="L95" s="7" t="s">
+      <c r="M95" s="7" t="s">
         <v>556</v>
       </c>
-      <c r="M95" s="8" t="s">
+      <c r="N95" s="8" t="s">
         <v>839</v>
       </c>
-      <c r="N95" s="8" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="96" spans="1:14" ht="15.6">
+      <c r="O95" s="8" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="96" spans="1:15" ht="16.2" thickBot="1">
       <c r="A96" s="5" t="s">
         <v>557</v>
       </c>
@@ -7095,20 +7444,23 @@
       <c r="J96" s="10" t="s">
         <v>704</v>
       </c>
-      <c r="K96" s="10" t="s">
+      <c r="K96" s="26" t="s">
+        <v>848</v>
+      </c>
+      <c r="L96" s="10" t="s">
         <v>362</v>
       </c>
-      <c r="L96" s="7" t="s">
+      <c r="M96" s="7" t="s">
         <v>562</v>
       </c>
-      <c r="M96" s="8" t="s">
+      <c r="N96" s="8" t="s">
         <v>840</v>
       </c>
-      <c r="N96" s="8" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="97" spans="1:14" ht="15.6">
+      <c r="O96" s="8" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="97" spans="1:15" ht="16.2" thickBot="1">
       <c r="A97" s="5" t="s">
         <v>563</v>
       </c>
@@ -7137,20 +7489,23 @@
       <c r="J97" s="10" t="s">
         <v>705</v>
       </c>
-      <c r="K97" s="10" t="s">
+      <c r="K97" s="26" t="s">
+        <v>848</v>
+      </c>
+      <c r="L97" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="L97" s="7" t="s">
+      <c r="M97" s="7" t="s">
         <v>567</v>
       </c>
-      <c r="M97" s="8" t="s">
+      <c r="N97" s="8" t="s">
         <v>841</v>
       </c>
-      <c r="N97" s="8" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="98" spans="1:14" ht="15.6">
+      <c r="O97" s="8" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="98" spans="1:15" ht="16.2" thickBot="1">
       <c r="A98" s="5" t="s">
         <v>568</v>
       </c>
@@ -7179,20 +7534,23 @@
       <c r="J98" s="10" t="s">
         <v>705</v>
       </c>
-      <c r="K98" s="10" t="s">
+      <c r="K98" s="26" t="s">
+        <v>848</v>
+      </c>
+      <c r="L98" s="10" t="s">
         <v>251</v>
       </c>
-      <c r="L98" s="7" t="s">
+      <c r="M98" s="7" t="s">
         <v>572</v>
       </c>
-      <c r="M98" s="8" t="s">
+      <c r="N98" s="8" t="s">
         <v>842</v>
       </c>
-      <c r="N98" s="8" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="99" spans="1:14" ht="15.6">
+      <c r="O98" s="8" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="99" spans="1:15" ht="16.2" thickBot="1">
       <c r="A99" s="5" t="s">
         <v>573</v>
       </c>
@@ -7221,20 +7579,23 @@
       <c r="J99" s="10" t="s">
         <v>706</v>
       </c>
-      <c r="K99" s="10" t="s">
+      <c r="K99" s="26" t="s">
+        <v>849</v>
+      </c>
+      <c r="L99" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="L99" s="7" t="s">
+      <c r="M99" s="7" t="s">
         <v>578</v>
       </c>
-      <c r="M99" s="8" t="s">
+      <c r="N99" s="8" t="s">
         <v>843</v>
       </c>
-      <c r="N99" s="8" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="100" spans="1:14" ht="15.6">
+      <c r="O99" s="8" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="100" spans="1:15" ht="16.2" thickBot="1">
       <c r="A100" s="5" t="s">
         <v>579</v>
       </c>
@@ -7263,20 +7624,23 @@
       <c r="J100" s="10" t="s">
         <v>582</v>
       </c>
-      <c r="K100" s="10" t="s">
+      <c r="K100" s="26" t="s">
+        <v>848</v>
+      </c>
+      <c r="L100" s="10" t="s">
         <v>385</v>
       </c>
-      <c r="L100" s="7" t="s">
+      <c r="M100" s="7" t="s">
         <v>583</v>
       </c>
-      <c r="M100" s="8" t="s">
+      <c r="N100" s="8" t="s">
         <v>844</v>
       </c>
-      <c r="N100" s="8" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="101" spans="1:14" ht="15.6">
+      <c r="O100" s="8" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="101" spans="1:15" ht="16.2" thickBot="1">
       <c r="A101" s="5" t="s">
         <v>584</v>
       </c>
@@ -7305,20 +7669,23 @@
       <c r="J101" s="10" t="s">
         <v>707</v>
       </c>
-      <c r="K101" s="10" t="s">
+      <c r="K101" s="26" t="s">
+        <v>848</v>
+      </c>
+      <c r="L101" s="10" t="s">
         <v>362</v>
       </c>
-      <c r="L101" s="7" t="s">
+      <c r="M101" s="7" t="s">
         <v>587</v>
       </c>
-      <c r="M101" s="8" t="s">
+      <c r="N101" s="8" t="s">
         <v>845</v>
       </c>
-      <c r="N101" s="8" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="102" spans="1:14" ht="15.6">
+      <c r="O101" s="8" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="102" spans="1:15" ht="16.2" thickBot="1">
       <c r="A102" s="5" t="s">
         <v>588</v>
       </c>
@@ -7347,122 +7714,125 @@
       <c r="J102" s="10" t="s">
         <v>591</v>
       </c>
-      <c r="K102" s="10" t="s">
+      <c r="K102" s="26" t="s">
+        <v>849</v>
+      </c>
+      <c r="L102" s="10" t="s">
         <v>385</v>
       </c>
-      <c r="L102" s="7" t="s">
+      <c r="M102" s="7" t="s">
         <v>592</v>
       </c>
-      <c r="M102" s="8" t="s">
+      <c r="N102" s="8" t="s">
         <v>846</v>
       </c>
-      <c r="N102" s="8" t="s">
+      <c r="O102" s="8" t="s">
         <v>599</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="L2" r:id="rId1" xr:uid="{E6A01206-11AB-4712-B68C-03D44C56E494}"/>
-    <hyperlink ref="L3" r:id="rId2" display="https://maps,app,goo,gl/qCB3ZkrDsyC6NYiH6" xr:uid="{0733B04F-1D08-4F0C-B17D-D0A5E196A691}"/>
-    <hyperlink ref="L4" r:id="rId3" display="https://maps,app,goo,gl/Yp6azA6JEvDwG4Lw5" xr:uid="{73E48E31-4ABA-4175-BF60-1E83F9638691}"/>
-    <hyperlink ref="L5" r:id="rId4" display="https://maps,app,goo,gl/JhUvG1EjmS8cLSR56" xr:uid="{F3DD2FFC-5863-41D9-A53E-BA19F18C799C}"/>
-    <hyperlink ref="L6" r:id="rId5" display="https://maps,app,goo,gl/H6roYdMGmqRyss9v6" xr:uid="{EEB2AA07-92F7-4D7D-8A14-50EE458AEA45}"/>
-    <hyperlink ref="L7" r:id="rId6" display="https://maps,app,goo,gl/cKdyjnwHdGnZLGsh8" xr:uid="{C44ED9DA-F5AF-4FF6-B43F-B1F39157C372}"/>
-    <hyperlink ref="L8" r:id="rId7" display="https://maps,app,goo,gl/mp2t7E98F4m1rVFQA" xr:uid="{87C8E288-DE8E-4CEA-8F35-9C8C5D81BC8D}"/>
-    <hyperlink ref="L9" r:id="rId8" display="https://maps,app,goo,gl/14zyeWePSJaDCbx96" xr:uid="{A8C61234-6C1B-4AAD-96A3-89A4F0A4252E}"/>
-    <hyperlink ref="L10" r:id="rId9" display="https://maps,app,goo,gl/wweSrBCi8yzqQZu99" xr:uid="{8CE56236-B692-4BA2-8BBC-2BD8434A1E88}"/>
-    <hyperlink ref="L11" r:id="rId10" display="https://maps,app,goo,gl/6rhxs5gb5Q5QdeAi9" xr:uid="{5B682EFD-923A-48E0-BBC2-069AA852D322}"/>
-    <hyperlink ref="L12" r:id="rId11" display="https://maps,app,goo,gl/RqmWcuMGpiLk8VUY6" xr:uid="{B0A39CAF-DC58-4C23-B4AE-0ADAEB1A00A4}"/>
-    <hyperlink ref="L13" r:id="rId12" display="https://maps,app,goo,gl/eQP3N6Yf7R1fcukH8" xr:uid="{6869005E-E324-4C6A-A293-65A529B9A811}"/>
-    <hyperlink ref="L14" r:id="rId13" display="https://maps,app,goo,gl/nhn3EnRs8NJksUUJ9" xr:uid="{0D7FACA9-BA7D-4CB6-AF8C-67A50F3E694C}"/>
-    <hyperlink ref="L15" r:id="rId14" display="https://maps,app,goo,gl/euiJNii4JSBBDtwe9" xr:uid="{07D1CC95-DAEA-4376-BD10-2DEC75515AF9}"/>
-    <hyperlink ref="L16" r:id="rId15" display="https://maps,app,goo,gl/dqEgErHYTZ6bN9XJ9" xr:uid="{53BF6CA8-7BF0-48C2-96A2-4752A2FDF5F4}"/>
-    <hyperlink ref="L17" r:id="rId16" display="https://maps,app,goo,gl/fdha22q564CX9Uvx7" xr:uid="{5DA1610C-A78E-4CAA-8627-368F72253F89}"/>
-    <hyperlink ref="L18" r:id="rId17" display="https://maps,app,goo,gl/A1Zor3PMzwxLNMTP7" xr:uid="{830B3418-F963-4A15-ADC6-4961C5521903}"/>
-    <hyperlink ref="L19" r:id="rId18" display="https://maps,app,goo,gl/z85JmpmHUoCWpxA18" xr:uid="{64923DDA-D140-4536-8F68-0AB0D440A9A7}"/>
-    <hyperlink ref="L20" r:id="rId19" display="https://maps,app,goo,gl/ynaMTj7a6qbS7bUz8" xr:uid="{160ACF00-C152-4BFA-8BAD-27D0BB9811CA}"/>
-    <hyperlink ref="L21" r:id="rId20" display="https://maps,app,goo,gl/mZWDff8uReoLwG2b6" xr:uid="{15AAF458-E572-40DA-BAB9-E429203EF370}"/>
-    <hyperlink ref="L22" r:id="rId21" display="https://maps,app,goo,gl/rxQc7DTHgLbGxnFq5" xr:uid="{FDDD16FC-3FD8-46CD-8B84-BD7B3A529BF7}"/>
-    <hyperlink ref="L23" r:id="rId22" display="https://maps,app,goo,gl/5kg8Ehaq3LheiMkE6" xr:uid="{C3737FF0-752F-4B1E-8C48-C270A0E3EFF5}"/>
-    <hyperlink ref="L24" r:id="rId23" display="https://maps,app,goo,gl/r9s6fYSuzg82J8yS8" xr:uid="{E66B1859-A21D-49A8-A718-0661CA79F79E}"/>
-    <hyperlink ref="L25" r:id="rId24" display="https://maps,app,goo,gl/gxYh2XCQzFwq4npB9" xr:uid="{ED222F20-BA39-4D90-BF28-D0DF156FD0CD}"/>
-    <hyperlink ref="L26" r:id="rId25" display="https://maps,app,goo,gl/zYkmWfvNjSbUp3Eu6" xr:uid="{5E474D6D-FF2B-4A22-AC95-5022B115EB3D}"/>
-    <hyperlink ref="L27" r:id="rId26" xr:uid="{7B4E7060-A3E1-44F0-82A0-970EE73530AD}"/>
-    <hyperlink ref="L28" r:id="rId27" display="https://maps,app,goo,gl/oWjxS475BwBSr2fw9" xr:uid="{A76D009F-764F-440D-B3FA-89587D360408}"/>
-    <hyperlink ref="L29" r:id="rId28" display="https://maps,app,goo,gl/ePoXhbEtywJu18rR8" xr:uid="{A957CD70-F7E7-493A-92FC-448B6B71E89B}"/>
-    <hyperlink ref="L30" r:id="rId29" display="https://maps,app,goo,gl/pkYzpFj9W8m5tY6t5" xr:uid="{A52DDB38-634B-4B1D-82EA-61982E1CD69B}"/>
-    <hyperlink ref="L31" r:id="rId30" display="https://maps,app,goo,gl/bB7nfAMAC8ATmFCx6" xr:uid="{5755B3D3-8EF6-4248-A073-E8535F1F6AAF}"/>
-    <hyperlink ref="L32" r:id="rId31" display="https://maps,app,goo,gl/EWapRReCY6Pr62ht6" xr:uid="{88E17DA4-C006-4929-AD75-D994C8F53DD3}"/>
-    <hyperlink ref="L33" r:id="rId32" display="https://maps,app,goo,gl/qapSr9hGm21GGjbX9" xr:uid="{98D551BE-8182-4C34-B90E-7404971959AD}"/>
-    <hyperlink ref="L34" r:id="rId33" xr:uid="{CC9EDAAD-530B-4FC9-A821-D9A982D70FD3}"/>
-    <hyperlink ref="L35" r:id="rId34" xr:uid="{4BB2EA78-BF1D-48F4-9202-793021387FF0}"/>
-    <hyperlink ref="L36" r:id="rId35" xr:uid="{0E6FAE56-41FF-4A94-B528-67DC6EF2FE1C}"/>
-    <hyperlink ref="L37" r:id="rId36" xr:uid="{FB431361-8160-47F2-A73B-1E5E6399BB99}"/>
-    <hyperlink ref="L38" r:id="rId37" xr:uid="{88751F84-BFB9-4177-8FBC-5518E1691F23}"/>
-    <hyperlink ref="L39" r:id="rId38" xr:uid="{0C3DD1E1-8EFD-4CB5-96B3-E5F2E39CAA65}"/>
-    <hyperlink ref="L40" r:id="rId39" xr:uid="{FC8467C0-3CCB-4930-A941-C68C977257D1}"/>
-    <hyperlink ref="L41" r:id="rId40" xr:uid="{542A617E-5AFF-4EE3-856E-7DABA745DC19}"/>
-    <hyperlink ref="L42" r:id="rId41" xr:uid="{CC5260FA-7C14-4415-B983-E8CD2CE6C53D}"/>
-    <hyperlink ref="L43" r:id="rId42" xr:uid="{5EF44071-1A13-4C81-B5CA-81DDA4A1E88E}"/>
-    <hyperlink ref="L44" r:id="rId43" display="https://maps,app,goo,gl/6C2FMYL3sF67TKkP9" xr:uid="{ED36C6E8-EE6F-4A7A-AEA0-CD01EBF24CA4}"/>
-    <hyperlink ref="L45" r:id="rId44" display="https://maps,app,goo,gl/ob21PD5urtma2mmf8" xr:uid="{6C372D71-E51A-4489-9B61-CDB19E7B762C}"/>
-    <hyperlink ref="L46" r:id="rId45" display="https://maps,app,goo,gl/E3pUdfMfBtPh8Nkw7" xr:uid="{A78F6760-8510-4CE1-912F-66701E7321AF}"/>
-    <hyperlink ref="L47" r:id="rId46" display="https://maps,app,goo,gl/CSGcNJAKNCZB9o3S9" xr:uid="{CF8357D3-FD99-4D56-99E3-A181D39123EA}"/>
-    <hyperlink ref="L48" r:id="rId47" display="https://maps,app,goo,gl/DSuSCv2RMzzZq5cL9" xr:uid="{194516BC-2ABF-412B-B381-44BA4E139ADF}"/>
-    <hyperlink ref="L49" r:id="rId48" display="https://maps,app,goo,gl/jskCYxWfVhJ6H1Cf8" xr:uid="{82A5847F-E4F1-4919-B0CE-1FB9A5CF465A}"/>
-    <hyperlink ref="L50" r:id="rId49" xr:uid="{6D3C7A56-29F5-4871-B528-5933F794938F}"/>
-    <hyperlink ref="L51" r:id="rId50" xr:uid="{EB674118-96A2-43EA-8E0C-1C8C758BA5FF}"/>
-    <hyperlink ref="L52" r:id="rId51" xr:uid="{17AC1E6E-935F-4DD1-A57D-2DBCF50F27A1}"/>
-    <hyperlink ref="L53" r:id="rId52" xr:uid="{AEB98000-BCBA-4E50-94E5-658397A38298}"/>
-    <hyperlink ref="L54" r:id="rId53" xr:uid="{B9DDAC1C-B096-421E-980E-1499E69A8459}"/>
-    <hyperlink ref="L55" r:id="rId54" xr:uid="{9849DDFD-2E8F-49C0-B7A7-B351EC4FC663}"/>
-    <hyperlink ref="L56" r:id="rId55" xr:uid="{88C9AFBE-3F15-4417-924B-C706611D1D77}"/>
-    <hyperlink ref="L57" r:id="rId56" xr:uid="{9399421F-7C34-45D1-A329-E793D00735F9}"/>
-    <hyperlink ref="L58" r:id="rId57" xr:uid="{563EB96C-D404-4364-9E74-B6F7FB3C04E4}"/>
-    <hyperlink ref="L59" r:id="rId58" xr:uid="{6BF6371A-F5F1-4FAE-B23B-36896B72C511}"/>
-    <hyperlink ref="L60" r:id="rId59" xr:uid="{56369DB2-0001-4426-A77A-D097EF4F436A}"/>
-    <hyperlink ref="L61" r:id="rId60" xr:uid="{038F4637-AFEE-4771-A03A-A6399810416B}"/>
-    <hyperlink ref="L62" r:id="rId61" xr:uid="{5C96AFE6-C76F-4314-B7DB-C0FDCD3E4421}"/>
-    <hyperlink ref="L63" r:id="rId62" xr:uid="{598B1018-4284-40D4-BE97-D6A24F2C200F}"/>
-    <hyperlink ref="L64" r:id="rId63" xr:uid="{F275C1F8-9FC0-4FEE-8E3B-7F779BF42424}"/>
-    <hyperlink ref="L65" r:id="rId64" xr:uid="{E4A0CF80-C564-444F-B6B5-EDBF311C4A2B}"/>
-    <hyperlink ref="L66" r:id="rId65" xr:uid="{A7765BE9-1AC7-45A3-B1FC-D4E1D651CA42}"/>
-    <hyperlink ref="L67" r:id="rId66" xr:uid="{469F039D-48A5-4546-8C5D-5060E8892B29}"/>
-    <hyperlink ref="L68" r:id="rId67" xr:uid="{AC8559A3-9440-42C3-8635-4A45210F7855}"/>
-    <hyperlink ref="L69" r:id="rId68" xr:uid="{297EFDDD-EF4A-4FB8-A709-82D53E1F929D}"/>
-    <hyperlink ref="L70" r:id="rId69" xr:uid="{1526D6DC-95DF-48B7-AF91-128F83916034}"/>
-    <hyperlink ref="L71" r:id="rId70" xr:uid="{CBA9A167-AD3E-42D1-9B4F-66CB7D1DE6F5}"/>
-    <hyperlink ref="L72" r:id="rId71" xr:uid="{6495EC6E-7E8D-4778-8739-6484B0449122}"/>
-    <hyperlink ref="L73" r:id="rId72" xr:uid="{38E7B74F-3C76-427C-9E23-E50CECE70BF6}"/>
-    <hyperlink ref="L74" r:id="rId73" xr:uid="{041ACE33-DDD7-4B92-A58F-092CE033A7F3}"/>
-    <hyperlink ref="L75" r:id="rId74" xr:uid="{6C985AEC-B436-48B2-8C15-E86F6A099EE0}"/>
-    <hyperlink ref="L76" r:id="rId75" xr:uid="{0740AED8-64A6-4B48-88B7-2DB4AA718846}"/>
-    <hyperlink ref="L77" r:id="rId76" xr:uid="{42F2A67D-4964-47F1-8EF6-781E994ABC75}"/>
-    <hyperlink ref="L78" r:id="rId77" xr:uid="{88111CA1-E755-4F82-9DA6-FDB30F3AA4AC}"/>
-    <hyperlink ref="L79" r:id="rId78" xr:uid="{86C84AF5-4C2E-4C33-906B-2173D06B4FB2}"/>
-    <hyperlink ref="L80" r:id="rId79" xr:uid="{0AEFFC6C-24D6-4D91-9FB5-2500BA5B4EBC}"/>
-    <hyperlink ref="L81" r:id="rId80" xr:uid="{2D5262B4-5873-4F07-AD44-B76C464F6F53}"/>
-    <hyperlink ref="L82" r:id="rId81" xr:uid="{0669FE8D-C7A6-4E98-BA25-1139F7BE2B08}"/>
-    <hyperlink ref="L83" r:id="rId82" xr:uid="{435A2292-B116-4168-8E7C-8528C1A174BC}"/>
-    <hyperlink ref="L84" r:id="rId83" xr:uid="{FEEFF606-6E9A-41F4-A06C-7E02BDF84F1A}"/>
-    <hyperlink ref="L85" r:id="rId84" xr:uid="{5A8C991F-CB9D-4B39-83D3-EE8AD4BCF8FF}"/>
-    <hyperlink ref="L86" r:id="rId85" xr:uid="{67AE2021-4B72-40EE-A006-09FCFD34CAD2}"/>
-    <hyperlink ref="L87" r:id="rId86" xr:uid="{DE850BB0-2BEC-4C4E-B1D4-0BE0A3E4C565}"/>
-    <hyperlink ref="L88" r:id="rId87" xr:uid="{5EF17A3E-0B4C-4E89-9E95-BB4B7BBD9131}"/>
-    <hyperlink ref="L89" r:id="rId88" xr:uid="{12E55A71-A877-4B8B-BA03-A1F9FA869C1A}"/>
-    <hyperlink ref="L90" r:id="rId89" xr:uid="{9873BB3A-730F-429B-8A12-7DF85AEB652F}"/>
-    <hyperlink ref="L91" r:id="rId90" xr:uid="{DD6F3987-C7B9-43B1-A716-3D25D077CFB4}"/>
-    <hyperlink ref="L92" r:id="rId91" xr:uid="{A02CC1F9-934B-4CD7-8BF2-3EE5B414D366}"/>
-    <hyperlink ref="L93" r:id="rId92" xr:uid="{A72E4B5A-C723-48FC-A271-BB342F12CB20}"/>
-    <hyperlink ref="L94" r:id="rId93" xr:uid="{FA881DCB-99BD-4CFF-8CA1-86ECE0EB97A2}"/>
-    <hyperlink ref="L95" r:id="rId94" xr:uid="{AA5EC6F9-3232-4EBE-801C-ADE588E64C19}"/>
-    <hyperlink ref="L96" r:id="rId95" xr:uid="{77E8DF6E-9C7A-41D4-87B6-473B970814AB}"/>
-    <hyperlink ref="L97" r:id="rId96" xr:uid="{72BB0186-E744-4C15-8E80-89E5BA2AFC3F}"/>
-    <hyperlink ref="L98" r:id="rId97" xr:uid="{CE8EDAB8-0040-445A-AE44-B96FF9636B15}"/>
-    <hyperlink ref="L99" r:id="rId98" xr:uid="{20C873C0-BB00-4F8E-8428-AFB60824F631}"/>
-    <hyperlink ref="L100" r:id="rId99" xr:uid="{25982ADF-8870-48BA-BE82-F5159FA5620D}"/>
-    <hyperlink ref="L101" r:id="rId100" xr:uid="{EC17C9A9-B429-4A8E-B8DD-14DD7119D92C}"/>
-    <hyperlink ref="L102" r:id="rId101" xr:uid="{8DD308E4-9E4F-4B4A-A9DB-00EAD7ED5727}"/>
+    <hyperlink ref="M2" r:id="rId1" xr:uid="{E6A01206-11AB-4712-B68C-03D44C56E494}"/>
+    <hyperlink ref="M3" r:id="rId2" display="https://maps,app,goo,gl/qCB3ZkrDsyC6NYiH6" xr:uid="{0733B04F-1D08-4F0C-B17D-D0A5E196A691}"/>
+    <hyperlink ref="M4" r:id="rId3" display="https://maps,app,goo,gl/Yp6azA6JEvDwG4Lw5" xr:uid="{73E48E31-4ABA-4175-BF60-1E83F9638691}"/>
+    <hyperlink ref="M5" r:id="rId4" display="https://maps,app,goo,gl/JhUvG1EjmS8cLSR56" xr:uid="{F3DD2FFC-5863-41D9-A53E-BA19F18C799C}"/>
+    <hyperlink ref="M6" r:id="rId5" display="https://maps,app,goo,gl/H6roYdMGmqRyss9v6" xr:uid="{EEB2AA07-92F7-4D7D-8A14-50EE458AEA45}"/>
+    <hyperlink ref="M7" r:id="rId6" display="https://maps,app,goo,gl/cKdyjnwHdGnZLGsh8" xr:uid="{C44ED9DA-F5AF-4FF6-B43F-B1F39157C372}"/>
+    <hyperlink ref="M8" r:id="rId7" display="https://maps,app,goo,gl/mp2t7E98F4m1rVFQA" xr:uid="{87C8E288-DE8E-4CEA-8F35-9C8C5D81BC8D}"/>
+    <hyperlink ref="M9" r:id="rId8" display="https://maps,app,goo,gl/14zyeWePSJaDCbx96" xr:uid="{A8C61234-6C1B-4AAD-96A3-89A4F0A4252E}"/>
+    <hyperlink ref="M10" r:id="rId9" display="https://maps,app,goo,gl/wweSrBCi8yzqQZu99" xr:uid="{8CE56236-B692-4BA2-8BBC-2BD8434A1E88}"/>
+    <hyperlink ref="M11" r:id="rId10" display="https://maps,app,goo,gl/6rhxs5gb5Q5QdeAi9" xr:uid="{5B682EFD-923A-48E0-BBC2-069AA852D322}"/>
+    <hyperlink ref="M12" r:id="rId11" display="https://maps,app,goo,gl/RqmWcuMGpiLk8VUY6" xr:uid="{B0A39CAF-DC58-4C23-B4AE-0ADAEB1A00A4}"/>
+    <hyperlink ref="M13" r:id="rId12" display="https://maps,app,goo,gl/eQP3N6Yf7R1fcukH8" xr:uid="{6869005E-E324-4C6A-A293-65A529B9A811}"/>
+    <hyperlink ref="M14" r:id="rId13" display="https://maps,app,goo,gl/nhn3EnRs8NJksUUJ9" xr:uid="{0D7FACA9-BA7D-4CB6-AF8C-67A50F3E694C}"/>
+    <hyperlink ref="M15" r:id="rId14" display="https://maps,app,goo,gl/euiJNii4JSBBDtwe9" xr:uid="{07D1CC95-DAEA-4376-BD10-2DEC75515AF9}"/>
+    <hyperlink ref="M16" r:id="rId15" display="https://maps,app,goo,gl/dqEgErHYTZ6bN9XJ9" xr:uid="{53BF6CA8-7BF0-48C2-96A2-4752A2FDF5F4}"/>
+    <hyperlink ref="M17" r:id="rId16" display="https://maps,app,goo,gl/fdha22q564CX9Uvx7" xr:uid="{5DA1610C-A78E-4CAA-8627-368F72253F89}"/>
+    <hyperlink ref="M18" r:id="rId17" display="https://maps,app,goo,gl/A1Zor3PMzwxLNMTP7" xr:uid="{830B3418-F963-4A15-ADC6-4961C5521903}"/>
+    <hyperlink ref="M19" r:id="rId18" display="https://maps,app,goo,gl/z85JmpmHUoCWpxA18" xr:uid="{64923DDA-D140-4536-8F68-0AB0D440A9A7}"/>
+    <hyperlink ref="M20" r:id="rId19" display="https://maps,app,goo,gl/ynaMTj7a6qbS7bUz8" xr:uid="{160ACF00-C152-4BFA-8BAD-27D0BB9811CA}"/>
+    <hyperlink ref="M21" r:id="rId20" display="https://maps,app,goo,gl/mZWDff8uReoLwG2b6" xr:uid="{15AAF458-E572-40DA-BAB9-E429203EF370}"/>
+    <hyperlink ref="M22" r:id="rId21" display="https://maps,app,goo,gl/rxQc7DTHgLbGxnFq5" xr:uid="{FDDD16FC-3FD8-46CD-8B84-BD7B3A529BF7}"/>
+    <hyperlink ref="M23" r:id="rId22" display="https://maps,app,goo,gl/5kg8Ehaq3LheiMkE6" xr:uid="{C3737FF0-752F-4B1E-8C48-C270A0E3EFF5}"/>
+    <hyperlink ref="M24" r:id="rId23" display="https://maps,app,goo,gl/r9s6fYSuzg82J8yS8" xr:uid="{E66B1859-A21D-49A8-A718-0661CA79F79E}"/>
+    <hyperlink ref="M25" r:id="rId24" display="https://maps,app,goo,gl/gxYh2XCQzFwq4npB9" xr:uid="{ED222F20-BA39-4D90-BF28-D0DF156FD0CD}"/>
+    <hyperlink ref="M26" r:id="rId25" display="https://maps,app,goo,gl/zYkmWfvNjSbUp3Eu6" xr:uid="{5E474D6D-FF2B-4A22-AC95-5022B115EB3D}"/>
+    <hyperlink ref="M27" r:id="rId26" xr:uid="{7B4E7060-A3E1-44F0-82A0-970EE73530AD}"/>
+    <hyperlink ref="M28" r:id="rId27" display="https://maps,app,goo,gl/oWjxS475BwBSr2fw9" xr:uid="{A76D009F-764F-440D-B3FA-89587D360408}"/>
+    <hyperlink ref="M29" r:id="rId28" display="https://maps,app,goo,gl/ePoXhbEtywJu18rR8" xr:uid="{A957CD70-F7E7-493A-92FC-448B6B71E89B}"/>
+    <hyperlink ref="M30" r:id="rId29" display="https://maps,app,goo,gl/pkYzpFj9W8m5tY6t5" xr:uid="{A52DDB38-634B-4B1D-82EA-61982E1CD69B}"/>
+    <hyperlink ref="M31" r:id="rId30" display="https://maps,app,goo,gl/bB7nfAMAC8ATmFCx6" xr:uid="{5755B3D3-8EF6-4248-A073-E8535F1F6AAF}"/>
+    <hyperlink ref="M32" r:id="rId31" display="https://maps,app,goo,gl/EWapRReCY6Pr62ht6" xr:uid="{88E17DA4-C006-4929-AD75-D994C8F53DD3}"/>
+    <hyperlink ref="M33" r:id="rId32" display="https://maps,app,goo,gl/qapSr9hGm21GGjbX9" xr:uid="{98D551BE-8182-4C34-B90E-7404971959AD}"/>
+    <hyperlink ref="M34" r:id="rId33" xr:uid="{CC9EDAAD-530B-4FC9-A821-D9A982D70FD3}"/>
+    <hyperlink ref="M35" r:id="rId34" xr:uid="{4BB2EA78-BF1D-48F4-9202-793021387FF0}"/>
+    <hyperlink ref="M36" r:id="rId35" xr:uid="{0E6FAE56-41FF-4A94-B528-67DC6EF2FE1C}"/>
+    <hyperlink ref="M37" r:id="rId36" xr:uid="{FB431361-8160-47F2-A73B-1E5E6399BB99}"/>
+    <hyperlink ref="M38" r:id="rId37" xr:uid="{88751F84-BFB9-4177-8FBC-5518E1691F23}"/>
+    <hyperlink ref="M39" r:id="rId38" xr:uid="{0C3DD1E1-8EFD-4CB5-96B3-E5F2E39CAA65}"/>
+    <hyperlink ref="M40" r:id="rId39" xr:uid="{FC8467C0-3CCB-4930-A941-C68C977257D1}"/>
+    <hyperlink ref="M41" r:id="rId40" xr:uid="{542A617E-5AFF-4EE3-856E-7DABA745DC19}"/>
+    <hyperlink ref="M42" r:id="rId41" xr:uid="{CC5260FA-7C14-4415-B983-E8CD2CE6C53D}"/>
+    <hyperlink ref="M43" r:id="rId42" xr:uid="{5EF44071-1A13-4C81-B5CA-81DDA4A1E88E}"/>
+    <hyperlink ref="M44" r:id="rId43" display="https://maps,app,goo,gl/6C2FMYL3sF67TKkP9" xr:uid="{ED36C6E8-EE6F-4A7A-AEA0-CD01EBF24CA4}"/>
+    <hyperlink ref="M45" r:id="rId44" display="https://maps,app,goo,gl/ob21PD5urtma2mmf8" xr:uid="{6C372D71-E51A-4489-9B61-CDB19E7B762C}"/>
+    <hyperlink ref="M46" r:id="rId45" display="https://maps,app,goo,gl/E3pUdfMfBtPh8Nkw7" xr:uid="{A78F6760-8510-4CE1-912F-66701E7321AF}"/>
+    <hyperlink ref="M47" r:id="rId46" display="https://maps,app,goo,gl/CSGcNJAKNCZB9o3S9" xr:uid="{CF8357D3-FD99-4D56-99E3-A181D39123EA}"/>
+    <hyperlink ref="M48" r:id="rId47" display="https://maps,app,goo,gl/DSuSCv2RMzzZq5cL9" xr:uid="{194516BC-2ABF-412B-B381-44BA4E139ADF}"/>
+    <hyperlink ref="M49" r:id="rId48" display="https://maps,app,goo,gl/jskCYxWfVhJ6H1Cf8" xr:uid="{82A5847F-E4F1-4919-B0CE-1FB9A5CF465A}"/>
+    <hyperlink ref="M50" r:id="rId49" xr:uid="{6D3C7A56-29F5-4871-B528-5933F794938F}"/>
+    <hyperlink ref="M51" r:id="rId50" xr:uid="{EB674118-96A2-43EA-8E0C-1C8C758BA5FF}"/>
+    <hyperlink ref="M52" r:id="rId51" xr:uid="{17AC1E6E-935F-4DD1-A57D-2DBCF50F27A1}"/>
+    <hyperlink ref="M53" r:id="rId52" xr:uid="{AEB98000-BCBA-4E50-94E5-658397A38298}"/>
+    <hyperlink ref="M54" r:id="rId53" xr:uid="{B9DDAC1C-B096-421E-980E-1499E69A8459}"/>
+    <hyperlink ref="M55" r:id="rId54" xr:uid="{9849DDFD-2E8F-49C0-B7A7-B351EC4FC663}"/>
+    <hyperlink ref="M56" r:id="rId55" xr:uid="{88C9AFBE-3F15-4417-924B-C706611D1D77}"/>
+    <hyperlink ref="M57" r:id="rId56" xr:uid="{9399421F-7C34-45D1-A329-E793D00735F9}"/>
+    <hyperlink ref="M58" r:id="rId57" xr:uid="{563EB96C-D404-4364-9E74-B6F7FB3C04E4}"/>
+    <hyperlink ref="M59" r:id="rId58" xr:uid="{6BF6371A-F5F1-4FAE-B23B-36896B72C511}"/>
+    <hyperlink ref="M60" r:id="rId59" xr:uid="{56369DB2-0001-4426-A77A-D097EF4F436A}"/>
+    <hyperlink ref="M61" r:id="rId60" xr:uid="{038F4637-AFEE-4771-A03A-A6399810416B}"/>
+    <hyperlink ref="M62" r:id="rId61" xr:uid="{5C96AFE6-C76F-4314-B7DB-C0FDCD3E4421}"/>
+    <hyperlink ref="M63" r:id="rId62" xr:uid="{598B1018-4284-40D4-BE97-D6A24F2C200F}"/>
+    <hyperlink ref="M64" r:id="rId63" xr:uid="{F275C1F8-9FC0-4FEE-8E3B-7F779BF42424}"/>
+    <hyperlink ref="M65" r:id="rId64" xr:uid="{E4A0CF80-C564-444F-B6B5-EDBF311C4A2B}"/>
+    <hyperlink ref="M66" r:id="rId65" xr:uid="{A7765BE9-1AC7-45A3-B1FC-D4E1D651CA42}"/>
+    <hyperlink ref="M67" r:id="rId66" xr:uid="{469F039D-48A5-4546-8C5D-5060E8892B29}"/>
+    <hyperlink ref="M68" r:id="rId67" xr:uid="{AC8559A3-9440-42C3-8635-4A45210F7855}"/>
+    <hyperlink ref="M69" r:id="rId68" xr:uid="{297EFDDD-EF4A-4FB8-A709-82D53E1F929D}"/>
+    <hyperlink ref="M70" r:id="rId69" xr:uid="{1526D6DC-95DF-48B7-AF91-128F83916034}"/>
+    <hyperlink ref="M71" r:id="rId70" xr:uid="{CBA9A167-AD3E-42D1-9B4F-66CB7D1DE6F5}"/>
+    <hyperlink ref="M72" r:id="rId71" xr:uid="{6495EC6E-7E8D-4778-8739-6484B0449122}"/>
+    <hyperlink ref="M73" r:id="rId72" xr:uid="{38E7B74F-3C76-427C-9E23-E50CECE70BF6}"/>
+    <hyperlink ref="M74" r:id="rId73" xr:uid="{041ACE33-DDD7-4B92-A58F-092CE033A7F3}"/>
+    <hyperlink ref="M75" r:id="rId74" xr:uid="{6C985AEC-B436-48B2-8C15-E86F6A099EE0}"/>
+    <hyperlink ref="M76" r:id="rId75" xr:uid="{0740AED8-64A6-4B48-88B7-2DB4AA718846}"/>
+    <hyperlink ref="M77" r:id="rId76" xr:uid="{42F2A67D-4964-47F1-8EF6-781E994ABC75}"/>
+    <hyperlink ref="M78" r:id="rId77" xr:uid="{88111CA1-E755-4F82-9DA6-FDB30F3AA4AC}"/>
+    <hyperlink ref="M79" r:id="rId78" xr:uid="{86C84AF5-4C2E-4C33-906B-2173D06B4FB2}"/>
+    <hyperlink ref="M80" r:id="rId79" xr:uid="{0AEFFC6C-24D6-4D91-9FB5-2500BA5B4EBC}"/>
+    <hyperlink ref="M81" r:id="rId80" xr:uid="{2D5262B4-5873-4F07-AD44-B76C464F6F53}"/>
+    <hyperlink ref="M82" r:id="rId81" xr:uid="{0669FE8D-C7A6-4E98-BA25-1139F7BE2B08}"/>
+    <hyperlink ref="M83" r:id="rId82" xr:uid="{435A2292-B116-4168-8E7C-8528C1A174BC}"/>
+    <hyperlink ref="M84" r:id="rId83" xr:uid="{FEEFF606-6E9A-41F4-A06C-7E02BDF84F1A}"/>
+    <hyperlink ref="M85" r:id="rId84" xr:uid="{5A8C991F-CB9D-4B39-83D3-EE8AD4BCF8FF}"/>
+    <hyperlink ref="M86" r:id="rId85" xr:uid="{67AE2021-4B72-40EE-A006-09FCFD34CAD2}"/>
+    <hyperlink ref="M87" r:id="rId86" xr:uid="{DE850BB0-2BEC-4C4E-B1D4-0BE0A3E4C565}"/>
+    <hyperlink ref="M88" r:id="rId87" xr:uid="{5EF17A3E-0B4C-4E89-9E95-BB4B7BBD9131}"/>
+    <hyperlink ref="M89" r:id="rId88" xr:uid="{12E55A71-A877-4B8B-BA03-A1F9FA869C1A}"/>
+    <hyperlink ref="M90" r:id="rId89" xr:uid="{9873BB3A-730F-429B-8A12-7DF85AEB652F}"/>
+    <hyperlink ref="M91" r:id="rId90" xr:uid="{DD6F3987-C7B9-43B1-A716-3D25D077CFB4}"/>
+    <hyperlink ref="M92" r:id="rId91" xr:uid="{A02CC1F9-934B-4CD7-8BF2-3EE5B414D366}"/>
+    <hyperlink ref="M93" r:id="rId92" xr:uid="{A72E4B5A-C723-48FC-A271-BB342F12CB20}"/>
+    <hyperlink ref="M94" r:id="rId93" xr:uid="{FA881DCB-99BD-4CFF-8CA1-86ECE0EB97A2}"/>
+    <hyperlink ref="M95" r:id="rId94" xr:uid="{AA5EC6F9-3232-4EBE-801C-ADE588E64C19}"/>
+    <hyperlink ref="M96" r:id="rId95" xr:uid="{77E8DF6E-9C7A-41D4-87B6-473B970814AB}"/>
+    <hyperlink ref="M97" r:id="rId96" xr:uid="{72BB0186-E744-4C15-8E80-89E5BA2AFC3F}"/>
+    <hyperlink ref="M98" r:id="rId97" xr:uid="{CE8EDAB8-0040-445A-AE44-B96FF9636B15}"/>
+    <hyperlink ref="M99" r:id="rId98" xr:uid="{20C873C0-BB00-4F8E-8428-AFB60824F631}"/>
+    <hyperlink ref="M100" r:id="rId99" xr:uid="{25982ADF-8870-48BA-BE82-F5159FA5620D}"/>
+    <hyperlink ref="M101" r:id="rId100" xr:uid="{EC17C9A9-B429-4A8E-B8DD-14DD7119D92C}"/>
+    <hyperlink ref="M102" r:id="rId101" xr:uid="{8DD308E4-9E4F-4B4A-A9DB-00EAD7ED5727}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
